--- a/qaErrors/ig/StructureDefinition-fr-composition-document-ips.xlsx
+++ b/qaErrors/ig/StructureDefinition-fr-composition-document-ips.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-23T10:07:47+00:00</t>
+    <t>2026-09-23T11:10:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/qaErrors/ig/StructureDefinition-fr-composition-document-ips.xlsx
+++ b/qaErrors/ig/StructureDefinition-fr-composition-document-ips.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-23T11:10:32+00:00</t>
+    <t>2026-09-23T12:07:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/qaErrors/ig/StructureDefinition-fr-composition-document-ips.xlsx
+++ b/qaErrors/ig/StructureDefinition-fr-composition-document-ips.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$552</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$553</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20438" uniqueCount="1339">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20476" uniqueCount="1343">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-23T12:07:40+00:00</t>
+    <t>2026-09-24T11:21:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -3881,11 +3881,24 @@
     <t>historiqueGrossesse</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-observation-pregnancy-document|0.1.0|https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-observation-pregnancy-history-document|0.1.0)
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-observation-pregnancy-history-document|0.1.0)
 </t>
   </si>
   <si>
-    <t>Entrée Historique des grossesses ou Observation sur la grossesse</t>
+    <t>Entrée Historique des grossesses</t>
+  </si>
+  <si>
+    <t>Composition.section:sectionPregnancyHistory.entry:observationGrossesse</t>
+  </si>
+  <si>
+    <t>observationGrossesse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-observation-pregnancy-document|0.1.0)
+</t>
+  </si>
+  <si>
+    <t>Entrée Observation sur la grossesse</t>
   </si>
   <si>
     <t>Composition.section:sectionPregnancyHistory.emptyReason</t>
@@ -4557,7 +4570,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO552"/>
+  <dimension ref="A1:AO553"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="68.890625" customWidth="true" bestFit="true"/>
@@ -60811,14 +60824,16 @@
         <v>78</v>
       </c>
     </row>
-    <row r="482">
+    <row r="482" hidden="true">
       <c r="A482" t="s" s="2">
         <v>1229</v>
       </c>
       <c r="B482" t="s" s="2">
-        <v>881</v>
-      </c>
-      <c r="C482" s="2"/>
+        <v>874</v>
+      </c>
+      <c r="C482" t="s" s="2">
+        <v>1230</v>
+      </c>
       <c r="D482" t="s" s="2">
         <v>78</v>
       </c>
@@ -60827,10 +60842,10 @@
         <v>79</v>
       </c>
       <c r="G482" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H482" t="s" s="2">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="I482" t="s" s="2">
         <v>78</v>
@@ -60839,20 +60854,18 @@
         <v>78</v>
       </c>
       <c r="K482" t="s" s="2">
-        <v>235</v>
+        <v>1231</v>
       </c>
       <c r="L482" t="s" s="2">
-        <v>921</v>
+        <v>1232</v>
       </c>
       <c r="M482" t="s" s="2">
-        <v>883</v>
+        <v>876</v>
       </c>
       <c r="N482" t="s" s="2">
-        <v>884</v>
-      </c>
-      <c r="O482" t="s" s="2">
-        <v>885</v>
-      </c>
+        <v>877</v>
+      </c>
+      <c r="O482" s="2"/>
       <c r="P482" t="s" s="2">
         <v>78</v>
       </c>
@@ -60876,11 +60889,13 @@
         <v>78</v>
       </c>
       <c r="X482" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="Y482" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y482" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z482" t="s" s="2">
-        <v>887</v>
+        <v>78</v>
       </c>
       <c r="AA482" t="s" s="2">
         <v>78</v>
@@ -60898,13 +60913,13 @@
         <v>78</v>
       </c>
       <c r="AF482" t="s" s="2">
-        <v>881</v>
+        <v>874</v>
       </c>
       <c r="AG482" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH482" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI482" t="s" s="2">
         <v>878</v>
@@ -60916,10 +60931,10 @@
         <v>78</v>
       </c>
       <c r="AL482" t="s" s="2">
-        <v>888</v>
+        <v>879</v>
       </c>
       <c r="AM482" t="s" s="2">
-        <v>109</v>
+        <v>880</v>
       </c>
       <c r="AN482" t="s" s="2">
         <v>78</v>
@@ -60928,12 +60943,12 @@
         <v>78</v>
       </c>
     </row>
-    <row r="483" hidden="true">
+    <row r="483">
       <c r="A483" t="s" s="2">
-        <v>1230</v>
+        <v>1233</v>
       </c>
       <c r="B483" t="s" s="2">
-        <v>889</v>
+        <v>881</v>
       </c>
       <c r="C483" s="2"/>
       <c r="D483" t="s" s="2">
@@ -60944,10 +60959,10 @@
         <v>79</v>
       </c>
       <c r="G483" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H483" t="s" s="2">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="I483" t="s" s="2">
         <v>78</v>
@@ -60956,18 +60971,20 @@
         <v>78</v>
       </c>
       <c r="K483" t="s" s="2">
-        <v>81</v>
+        <v>235</v>
       </c>
       <c r="L483" t="s" s="2">
-        <v>890</v>
+        <v>921</v>
       </c>
       <c r="M483" t="s" s="2">
-        <v>891</v>
+        <v>883</v>
       </c>
       <c r="N483" t="s" s="2">
-        <v>892</v>
-      </c>
-      <c r="O483" s="2"/>
+        <v>884</v>
+      </c>
+      <c r="O483" t="s" s="2">
+        <v>885</v>
+      </c>
       <c r="P483" t="s" s="2">
         <v>78</v>
       </c>
@@ -60991,13 +61008,11 @@
         <v>78</v>
       </c>
       <c r="X483" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y483" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>175</v>
+      </c>
+      <c r="Y483" s="2"/>
       <c r="Z483" t="s" s="2">
-        <v>78</v>
+        <v>887</v>
       </c>
       <c r="AA483" t="s" s="2">
         <v>78</v>
@@ -61015,16 +61030,16 @@
         <v>78</v>
       </c>
       <c r="AF483" t="s" s="2">
-        <v>889</v>
+        <v>881</v>
       </c>
       <c r="AG483" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH483" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI483" t="s" s="2">
-        <v>856</v>
+        <v>878</v>
       </c>
       <c r="AJ483" t="s" s="2">
         <v>103</v>
@@ -61033,10 +61048,10 @@
         <v>78</v>
       </c>
       <c r="AL483" t="s" s="2">
-        <v>818</v>
+        <v>888</v>
       </c>
       <c r="AM483" t="s" s="2">
-        <v>893</v>
+        <v>109</v>
       </c>
       <c r="AN483" t="s" s="2">
         <v>78</v>
@@ -61045,16 +61060,14 @@
         <v>78</v>
       </c>
     </row>
-    <row r="484">
+    <row r="484" hidden="true">
       <c r="A484" t="s" s="2">
-        <v>1231</v>
+        <v>1234</v>
       </c>
       <c r="B484" t="s" s="2">
-        <v>812</v>
-      </c>
-      <c r="C484" t="s" s="2">
-        <v>1232</v>
-      </c>
+        <v>889</v>
+      </c>
+      <c r="C484" s="2"/>
       <c r="D484" t="s" s="2">
         <v>78</v>
       </c>
@@ -61063,10 +61076,10 @@
         <v>79</v>
       </c>
       <c r="G484" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H484" t="s" s="2">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="I484" t="s" s="2">
         <v>78</v>
@@ -61075,15 +61088,17 @@
         <v>78</v>
       </c>
       <c r="K484" t="s" s="2">
-        <v>568</v>
+        <v>81</v>
       </c>
       <c r="L484" t="s" s="2">
-        <v>1233</v>
+        <v>890</v>
       </c>
       <c r="M484" t="s" s="2">
-        <v>1234</v>
-      </c>
-      <c r="N484" s="2"/>
+        <v>891</v>
+      </c>
+      <c r="N484" t="s" s="2">
+        <v>892</v>
+      </c>
       <c r="O484" s="2"/>
       <c r="P484" t="s" s="2">
         <v>78</v>
@@ -61132,7 +61147,7 @@
         <v>78</v>
       </c>
       <c r="AF484" t="s" s="2">
-        <v>812</v>
+        <v>889</v>
       </c>
       <c r="AG484" t="s" s="2">
         <v>79</v>
@@ -61141,10 +61156,10 @@
         <v>80</v>
       </c>
       <c r="AI484" t="s" s="2">
-        <v>78</v>
+        <v>856</v>
       </c>
       <c r="AJ484" t="s" s="2">
-        <v>817</v>
+        <v>103</v>
       </c>
       <c r="AK484" t="s" s="2">
         <v>78</v>
@@ -61153,7 +61168,7 @@
         <v>818</v>
       </c>
       <c r="AM484" t="s" s="2">
-        <v>819</v>
+        <v>893</v>
       </c>
       <c r="AN484" t="s" s="2">
         <v>78</v>
@@ -61162,14 +61177,16 @@
         <v>78</v>
       </c>
     </row>
-    <row r="485" hidden="true">
+    <row r="485">
       <c r="A485" t="s" s="2">
         <v>1235</v>
       </c>
       <c r="B485" t="s" s="2">
-        <v>820</v>
-      </c>
-      <c r="C485" s="2"/>
+        <v>812</v>
+      </c>
+      <c r="C485" t="s" s="2">
+        <v>1236</v>
+      </c>
       <c r="D485" t="s" s="2">
         <v>78</v>
       </c>
@@ -61181,7 +61198,7 @@
         <v>91</v>
       </c>
       <c r="H485" t="s" s="2">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="I485" t="s" s="2">
         <v>78</v>
@@ -61190,13 +61207,13 @@
         <v>78</v>
       </c>
       <c r="K485" t="s" s="2">
-        <v>105</v>
+        <v>568</v>
       </c>
       <c r="L485" t="s" s="2">
-        <v>106</v>
+        <v>1237</v>
       </c>
       <c r="M485" t="s" s="2">
-        <v>107</v>
+        <v>1238</v>
       </c>
       <c r="N485" s="2"/>
       <c r="O485" s="2"/>
@@ -61247,28 +61264,28 @@
         <v>78</v>
       </c>
       <c r="AF485" t="s" s="2">
-        <v>108</v>
+        <v>812</v>
       </c>
       <c r="AG485" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH485" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI485" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ485" t="s" s="2">
-        <v>78</v>
+        <v>817</v>
       </c>
       <c r="AK485" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL485" t="s" s="2">
-        <v>109</v>
+        <v>818</v>
       </c>
       <c r="AM485" t="s" s="2">
-        <v>78</v>
+        <v>819</v>
       </c>
       <c r="AN485" t="s" s="2">
         <v>78</v>
@@ -61279,10 +61296,10 @@
     </row>
     <row r="486" hidden="true">
       <c r="A486" t="s" s="2">
-        <v>1236</v>
+        <v>1239</v>
       </c>
       <c r="B486" t="s" s="2">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="C486" s="2"/>
       <c r="D486" t="s" s="2">
@@ -61293,7 +61310,7 @@
         <v>79</v>
       </c>
       <c r="G486" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H486" t="s" s="2">
         <v>78</v>
@@ -61305,13 +61322,13 @@
         <v>78</v>
       </c>
       <c r="K486" t="s" s="2">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="L486" t="s" s="2">
-        <v>197</v>
+        <v>106</v>
       </c>
       <c r="M486" t="s" s="2">
-        <v>198</v>
+        <v>107</v>
       </c>
       <c r="N486" s="2"/>
       <c r="O486" s="2"/>
@@ -61350,35 +61367,37 @@
         <v>78</v>
       </c>
       <c r="AB486" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="AC486" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="AC486" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="AD486" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE486" t="s" s="2">
-        <v>118</v>
+        <v>78</v>
       </c>
       <c r="AF486" t="s" s="2">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="AG486" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH486" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI486" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ486" t="s" s="2">
-        <v>120</v>
+        <v>78</v>
       </c>
       <c r="AK486" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL486" t="s" s="2">
-        <v>78</v>
+        <v>109</v>
       </c>
       <c r="AM486" t="s" s="2">
         <v>78</v>
@@ -61392,14 +61411,12 @@
     </row>
     <row r="487" hidden="true">
       <c r="A487" t="s" s="2">
-        <v>1237</v>
+        <v>1240</v>
       </c>
       <c r="B487" t="s" s="2">
         <v>821</v>
       </c>
-      <c r="C487" t="s" s="2">
-        <v>405</v>
-      </c>
+      <c r="C487" s="2"/>
       <c r="D487" t="s" s="2">
         <v>78</v>
       </c>
@@ -61408,7 +61425,7 @@
         <v>79</v>
       </c>
       <c r="G487" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H487" t="s" s="2">
         <v>78</v>
@@ -61420,13 +61437,13 @@
         <v>78</v>
       </c>
       <c r="K487" t="s" s="2">
-        <v>407</v>
+        <v>112</v>
       </c>
       <c r="L487" t="s" s="2">
-        <v>823</v>
+        <v>197</v>
       </c>
       <c r="M487" t="s" s="2">
-        <v>408</v>
+        <v>198</v>
       </c>
       <c r="N487" s="2"/>
       <c r="O487" s="2"/>
@@ -61465,16 +61482,14 @@
         <v>78</v>
       </c>
       <c r="AB487" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC487" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>116</v>
+      </c>
+      <c r="AC487" s="2"/>
       <c r="AD487" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE487" t="s" s="2">
-        <v>78</v>
+        <v>118</v>
       </c>
       <c r="AF487" t="s" s="2">
         <v>119</v>
@@ -61486,7 +61501,7 @@
         <v>80</v>
       </c>
       <c r="AI487" t="s" s="2">
-        <v>207</v>
+        <v>78</v>
       </c>
       <c r="AJ487" t="s" s="2">
         <v>120</v>
@@ -61509,13 +61524,13 @@
     </row>
     <row r="488" hidden="true">
       <c r="A488" t="s" s="2">
-        <v>1238</v>
+        <v>1241</v>
       </c>
       <c r="B488" t="s" s="2">
         <v>821</v>
       </c>
       <c r="C488" t="s" s="2">
-        <v>825</v>
+        <v>405</v>
       </c>
       <c r="D488" t="s" s="2">
         <v>78</v>
@@ -61525,7 +61540,7 @@
         <v>79</v>
       </c>
       <c r="G488" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H488" t="s" s="2">
         <v>78</v>
@@ -61537,17 +61552,15 @@
         <v>78</v>
       </c>
       <c r="K488" t="s" s="2">
-        <v>826</v>
+        <v>407</v>
       </c>
       <c r="L488" t="s" s="2">
-        <v>827</v>
+        <v>823</v>
       </c>
       <c r="M488" t="s" s="2">
-        <v>828</v>
-      </c>
-      <c r="N488" t="s" s="2">
-        <v>829</v>
-      </c>
+        <v>408</v>
+      </c>
+      <c r="N488" s="2"/>
       <c r="O488" s="2"/>
       <c r="P488" t="s" s="2">
         <v>78</v>
@@ -61605,7 +61618,7 @@
         <v>80</v>
       </c>
       <c r="AI488" t="s" s="2">
-        <v>78</v>
+        <v>207</v>
       </c>
       <c r="AJ488" t="s" s="2">
         <v>120</v>
@@ -61628,14 +61641,16 @@
     </row>
     <row r="489" hidden="true">
       <c r="A489" t="s" s="2">
-        <v>1239</v>
+        <v>1242</v>
       </c>
       <c r="B489" t="s" s="2">
-        <v>830</v>
-      </c>
-      <c r="C489" s="2"/>
+        <v>821</v>
+      </c>
+      <c r="C489" t="s" s="2">
+        <v>825</v>
+      </c>
       <c r="D489" t="s" s="2">
-        <v>581</v>
+        <v>78</v>
       </c>
       <c r="E489" s="2"/>
       <c r="F489" t="s" s="2">
@@ -61648,26 +61663,24 @@
         <v>78</v>
       </c>
       <c r="I489" t="s" s="2">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="J489" t="s" s="2">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="K489" t="s" s="2">
-        <v>112</v>
+        <v>826</v>
       </c>
       <c r="L489" t="s" s="2">
-        <v>582</v>
+        <v>827</v>
       </c>
       <c r="M489" t="s" s="2">
-        <v>583</v>
+        <v>828</v>
       </c>
       <c r="N489" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="O489" t="s" s="2">
-        <v>412</v>
-      </c>
+        <v>829</v>
+      </c>
+      <c r="O489" s="2"/>
       <c r="P489" t="s" s="2">
         <v>78</v>
       </c>
@@ -61715,7 +61728,7 @@
         <v>78</v>
       </c>
       <c r="AF489" t="s" s="2">
-        <v>584</v>
+        <v>119</v>
       </c>
       <c r="AG489" t="s" s="2">
         <v>79</v>
@@ -61733,7 +61746,7 @@
         <v>78</v>
       </c>
       <c r="AL489" t="s" s="2">
-        <v>195</v>
+        <v>78</v>
       </c>
       <c r="AM489" t="s" s="2">
         <v>78</v>
@@ -61745,47 +61758,47 @@
         <v>78</v>
       </c>
     </row>
-    <row r="490">
+    <row r="490" hidden="true">
       <c r="A490" t="s" s="2">
-        <v>1240</v>
+        <v>1243</v>
       </c>
       <c r="B490" t="s" s="2">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="C490" s="2"/>
       <c r="D490" t="s" s="2">
-        <v>832</v>
+        <v>581</v>
       </c>
       <c r="E490" s="2"/>
       <c r="F490" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="G490" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H490" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I490" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="I490" t="s" s="2">
-        <v>78</v>
-      </c>
       <c r="J490" t="s" s="2">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="K490" t="s" s="2">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="L490" t="s" s="2">
-        <v>1241</v>
+        <v>582</v>
       </c>
       <c r="M490" t="s" s="2">
-        <v>834</v>
+        <v>583</v>
       </c>
       <c r="N490" t="s" s="2">
-        <v>835</v>
+        <v>115</v>
       </c>
       <c r="O490" t="s" s="2">
-        <v>836</v>
+        <v>412</v>
       </c>
       <c r="P490" t="s" s="2">
         <v>78</v>
@@ -61834,28 +61847,28 @@
         <v>78</v>
       </c>
       <c r="AF490" t="s" s="2">
-        <v>831</v>
+        <v>584</v>
       </c>
       <c r="AG490" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH490" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI490" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ490" t="s" s="2">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="AK490" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL490" t="s" s="2">
-        <v>556</v>
+        <v>195</v>
       </c>
       <c r="AM490" t="s" s="2">
-        <v>557</v>
+        <v>78</v>
       </c>
       <c r="AN490" t="s" s="2">
         <v>78</v>
@@ -61866,14 +61879,14 @@
     </row>
     <row r="491">
       <c r="A491" t="s" s="2">
-        <v>1242</v>
+        <v>1244</v>
       </c>
       <c r="B491" t="s" s="2">
-        <v>837</v>
+        <v>831</v>
       </c>
       <c r="C491" s="2"/>
       <c r="D491" t="s" s="2">
-        <v>78</v>
+        <v>832</v>
       </c>
       <c r="E491" s="2"/>
       <c r="F491" t="s" s="2">
@@ -61892,19 +61905,19 @@
         <v>78</v>
       </c>
       <c r="K491" t="s" s="2">
-        <v>235</v>
+        <v>105</v>
       </c>
       <c r="L491" t="s" s="2">
-        <v>838</v>
+        <v>1245</v>
       </c>
       <c r="M491" t="s" s="2">
-        <v>839</v>
+        <v>834</v>
       </c>
       <c r="N491" t="s" s="2">
-        <v>840</v>
+        <v>835</v>
       </c>
       <c r="O491" t="s" s="2">
-        <v>841</v>
+        <v>836</v>
       </c>
       <c r="P491" t="s" s="2">
         <v>78</v>
@@ -61914,7 +61927,7 @@
         <v>78</v>
       </c>
       <c r="S491" t="s" s="2">
-        <v>1243</v>
+        <v>78</v>
       </c>
       <c r="T491" t="s" s="2">
         <v>78</v>
@@ -61929,11 +61942,13 @@
         <v>78</v>
       </c>
       <c r="X491" t="s" s="2">
-        <v>325</v>
-      </c>
-      <c r="Y491" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y491" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z491" t="s" s="2">
-        <v>842</v>
+        <v>78</v>
       </c>
       <c r="AA491" t="s" s="2">
         <v>78</v>
@@ -61951,7 +61966,7 @@
         <v>78</v>
       </c>
       <c r="AF491" t="s" s="2">
-        <v>837</v>
+        <v>831</v>
       </c>
       <c r="AG491" t="s" s="2">
         <v>79</v>
@@ -61969,10 +61984,10 @@
         <v>78</v>
       </c>
       <c r="AL491" t="s" s="2">
-        <v>457</v>
+        <v>556</v>
       </c>
       <c r="AM491" t="s" s="2">
-        <v>458</v>
+        <v>557</v>
       </c>
       <c r="AN491" t="s" s="2">
         <v>78</v>
@@ -61981,12 +61996,12 @@
         <v>78</v>
       </c>
     </row>
-    <row r="492" hidden="true">
+    <row r="492">
       <c r="A492" t="s" s="2">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="B492" t="s" s="2">
-        <v>843</v>
+        <v>837</v>
       </c>
       <c r="C492" s="2"/>
       <c r="D492" t="s" s="2">
@@ -61994,13 +62009,13 @@
       </c>
       <c r="E492" s="2"/>
       <c r="F492" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="G492" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H492" t="s" s="2">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="I492" t="s" s="2">
         <v>78</v>
@@ -62009,17 +62024,19 @@
         <v>78</v>
       </c>
       <c r="K492" t="s" s="2">
-        <v>844</v>
+        <v>235</v>
       </c>
       <c r="L492" t="s" s="2">
-        <v>845</v>
+        <v>838</v>
       </c>
       <c r="M492" t="s" s="2">
-        <v>846</v>
-      </c>
-      <c r="N492" s="2"/>
+        <v>839</v>
+      </c>
+      <c r="N492" t="s" s="2">
+        <v>840</v>
+      </c>
       <c r="O492" t="s" s="2">
-        <v>536</v>
+        <v>841</v>
       </c>
       <c r="P492" t="s" s="2">
         <v>78</v>
@@ -62029,7 +62046,7 @@
         <v>78</v>
       </c>
       <c r="S492" t="s" s="2">
-        <v>78</v>
+        <v>1247</v>
       </c>
       <c r="T492" t="s" s="2">
         <v>78</v>
@@ -62044,13 +62061,11 @@
         <v>78</v>
       </c>
       <c r="X492" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y492" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>325</v>
+      </c>
+      <c r="Y492" s="2"/>
       <c r="Z492" t="s" s="2">
-        <v>78</v>
+        <v>842</v>
       </c>
       <c r="AA492" t="s" s="2">
         <v>78</v>
@@ -62068,13 +62083,13 @@
         <v>78</v>
       </c>
       <c r="AF492" t="s" s="2">
-        <v>843</v>
+        <v>837</v>
       </c>
       <c r="AG492" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH492" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI492" t="s" s="2">
         <v>78</v>
@@ -62086,24 +62101,24 @@
         <v>78</v>
       </c>
       <c r="AL492" t="s" s="2">
-        <v>538</v>
+        <v>457</v>
       </c>
       <c r="AM492" t="s" s="2">
-        <v>539</v>
+        <v>458</v>
       </c>
       <c r="AN492" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO492" t="s" s="2">
-        <v>541</v>
+        <v>78</v>
       </c>
     </row>
     <row r="493" hidden="true">
       <c r="A493" t="s" s="2">
-        <v>1245</v>
+        <v>1248</v>
       </c>
       <c r="B493" t="s" s="2">
-        <v>847</v>
+        <v>843</v>
       </c>
       <c r="C493" s="2"/>
       <c r="D493" t="s" s="2">
@@ -62114,7 +62129,7 @@
         <v>79</v>
       </c>
       <c r="G493" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H493" t="s" s="2">
         <v>78</v>
@@ -62126,18 +62141,18 @@
         <v>78</v>
       </c>
       <c r="K493" t="s" s="2">
-        <v>797</v>
+        <v>844</v>
       </c>
       <c r="L493" t="s" s="2">
-        <v>848</v>
+        <v>845</v>
       </c>
       <c r="M493" t="s" s="2">
-        <v>849</v>
-      </c>
-      <c r="N493" t="s" s="2">
-        <v>850</v>
-      </c>
-      <c r="O493" s="2"/>
+        <v>846</v>
+      </c>
+      <c r="N493" s="2"/>
+      <c r="O493" t="s" s="2">
+        <v>536</v>
+      </c>
       <c r="P493" t="s" s="2">
         <v>78</v>
       </c>
@@ -62185,13 +62200,13 @@
         <v>78</v>
       </c>
       <c r="AF493" t="s" s="2">
-        <v>847</v>
+        <v>843</v>
       </c>
       <c r="AG493" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH493" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI493" t="s" s="2">
         <v>78</v>
@@ -62203,24 +62218,24 @@
         <v>78</v>
       </c>
       <c r="AL493" t="s" s="2">
-        <v>78</v>
+        <v>538</v>
       </c>
       <c r="AM493" t="s" s="2">
-        <v>851</v>
+        <v>539</v>
       </c>
       <c r="AN493" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO493" t="s" s="2">
-        <v>78</v>
+        <v>541</v>
       </c>
     </row>
-    <row r="494">
+    <row r="494" hidden="true">
       <c r="A494" t="s" s="2">
-        <v>1246</v>
+        <v>1249</v>
       </c>
       <c r="B494" t="s" s="2">
-        <v>852</v>
+        <v>847</v>
       </c>
       <c r="C494" s="2"/>
       <c r="D494" t="s" s="2">
@@ -62228,13 +62243,13 @@
       </c>
       <c r="E494" s="2"/>
       <c r="F494" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="G494" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H494" t="s" s="2">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="I494" t="s" s="2">
         <v>78</v>
@@ -62243,16 +62258,16 @@
         <v>78</v>
       </c>
       <c r="K494" t="s" s="2">
-        <v>182</v>
+        <v>797</v>
       </c>
       <c r="L494" t="s" s="2">
-        <v>1247</v>
+        <v>848</v>
       </c>
       <c r="M494" t="s" s="2">
-        <v>854</v>
+        <v>849</v>
       </c>
       <c r="N494" t="s" s="2">
-        <v>855</v>
+        <v>850</v>
       </c>
       <c r="O494" s="2"/>
       <c r="P494" t="s" s="2">
@@ -62302,7 +62317,7 @@
         <v>78</v>
       </c>
       <c r="AF494" t="s" s="2">
-        <v>852</v>
+        <v>847</v>
       </c>
       <c r="AG494" t="s" s="2">
         <v>79</v>
@@ -62311,7 +62326,7 @@
         <v>91</v>
       </c>
       <c r="AI494" t="s" s="2">
-        <v>856</v>
+        <v>78</v>
       </c>
       <c r="AJ494" t="s" s="2">
         <v>103</v>
@@ -62320,10 +62335,10 @@
         <v>78</v>
       </c>
       <c r="AL494" t="s" s="2">
-        <v>857</v>
+        <v>78</v>
       </c>
       <c r="AM494" t="s" s="2">
-        <v>857</v>
+        <v>851</v>
       </c>
       <c r="AN494" t="s" s="2">
         <v>78</v>
@@ -62332,12 +62347,12 @@
         <v>78</v>
       </c>
     </row>
-    <row r="495" hidden="true">
+    <row r="495">
       <c r="A495" t="s" s="2">
-        <v>1248</v>
+        <v>1250</v>
       </c>
       <c r="B495" t="s" s="2">
-        <v>858</v>
+        <v>852</v>
       </c>
       <c r="C495" s="2"/>
       <c r="D495" t="s" s="2">
@@ -62345,13 +62360,13 @@
       </c>
       <c r="E495" s="2"/>
       <c r="F495" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="G495" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H495" t="s" s="2">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="I495" t="s" s="2">
         <v>78</v>
@@ -62360,20 +62375,18 @@
         <v>78</v>
       </c>
       <c r="K495" t="s" s="2">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="L495" t="s" s="2">
-        <v>859</v>
+        <v>1251</v>
       </c>
       <c r="M495" t="s" s="2">
-        <v>860</v>
+        <v>854</v>
       </c>
       <c r="N495" t="s" s="2">
-        <v>861</v>
-      </c>
-      <c r="O495" t="s" s="2">
-        <v>862</v>
-      </c>
+        <v>855</v>
+      </c>
+      <c r="O495" s="2"/>
       <c r="P495" t="s" s="2">
         <v>78</v>
       </c>
@@ -62397,13 +62410,13 @@
         <v>78</v>
       </c>
       <c r="X495" t="s" s="2">
-        <v>325</v>
+        <v>78</v>
       </c>
       <c r="Y495" t="s" s="2">
-        <v>863</v>
+        <v>78</v>
       </c>
       <c r="Z495" t="s" s="2">
-        <v>864</v>
+        <v>78</v>
       </c>
       <c r="AA495" t="s" s="2">
         <v>78</v>
@@ -62421,7 +62434,7 @@
         <v>78</v>
       </c>
       <c r="AF495" t="s" s="2">
-        <v>858</v>
+        <v>852</v>
       </c>
       <c r="AG495" t="s" s="2">
         <v>79</v>
@@ -62430,7 +62443,7 @@
         <v>91</v>
       </c>
       <c r="AI495" t="s" s="2">
-        <v>78</v>
+        <v>856</v>
       </c>
       <c r="AJ495" t="s" s="2">
         <v>103</v>
@@ -62439,24 +62452,24 @@
         <v>78</v>
       </c>
       <c r="AL495" t="s" s="2">
-        <v>865</v>
+        <v>857</v>
       </c>
       <c r="AM495" t="s" s="2">
-        <v>109</v>
+        <v>857</v>
       </c>
       <c r="AN495" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO495" t="s" s="2">
-        <v>460</v>
+        <v>78</v>
       </c>
     </row>
     <row r="496" hidden="true">
       <c r="A496" t="s" s="2">
-        <v>1249</v>
+        <v>1252</v>
       </c>
       <c r="B496" t="s" s="2">
-        <v>866</v>
+        <v>858</v>
       </c>
       <c r="C496" s="2"/>
       <c r="D496" t="s" s="2">
@@ -62479,19 +62492,19 @@
         <v>78</v>
       </c>
       <c r="K496" t="s" s="2">
-        <v>235</v>
+        <v>171</v>
       </c>
       <c r="L496" t="s" s="2">
-        <v>867</v>
+        <v>859</v>
       </c>
       <c r="M496" t="s" s="2">
-        <v>868</v>
+        <v>860</v>
       </c>
       <c r="N496" t="s" s="2">
-        <v>869</v>
+        <v>861</v>
       </c>
       <c r="O496" t="s" s="2">
-        <v>870</v>
+        <v>862</v>
       </c>
       <c r="P496" t="s" s="2">
         <v>78</v>
@@ -62516,13 +62529,13 @@
         <v>78</v>
       </c>
       <c r="X496" t="s" s="2">
-        <v>175</v>
+        <v>325</v>
       </c>
       <c r="Y496" t="s" s="2">
-        <v>871</v>
+        <v>863</v>
       </c>
       <c r="Z496" t="s" s="2">
-        <v>872</v>
+        <v>864</v>
       </c>
       <c r="AA496" t="s" s="2">
         <v>78</v>
@@ -62540,7 +62553,7 @@
         <v>78</v>
       </c>
       <c r="AF496" t="s" s="2">
-        <v>866</v>
+        <v>858</v>
       </c>
       <c r="AG496" t="s" s="2">
         <v>79</v>
@@ -62558,7 +62571,7 @@
         <v>78</v>
       </c>
       <c r="AL496" t="s" s="2">
-        <v>873</v>
+        <v>865</v>
       </c>
       <c r="AM496" t="s" s="2">
         <v>109</v>
@@ -62567,15 +62580,15 @@
         <v>78</v>
       </c>
       <c r="AO496" t="s" s="2">
-        <v>78</v>
+        <v>460</v>
       </c>
     </row>
     <row r="497" hidden="true">
       <c r="A497" t="s" s="2">
-        <v>1250</v>
+        <v>1253</v>
       </c>
       <c r="B497" t="s" s="2">
-        <v>874</v>
+        <v>866</v>
       </c>
       <c r="C497" s="2"/>
       <c r="D497" t="s" s="2">
@@ -62586,7 +62599,7 @@
         <v>79</v>
       </c>
       <c r="G497" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H497" t="s" s="2">
         <v>78</v>
@@ -62598,18 +62611,20 @@
         <v>78</v>
       </c>
       <c r="K497" t="s" s="2">
-        <v>797</v>
+        <v>235</v>
       </c>
       <c r="L497" t="s" s="2">
-        <v>875</v>
+        <v>867</v>
       </c>
       <c r="M497" t="s" s="2">
-        <v>876</v>
+        <v>868</v>
       </c>
       <c r="N497" t="s" s="2">
-        <v>877</v>
-      </c>
-      <c r="O497" s="2"/>
+        <v>869</v>
+      </c>
+      <c r="O497" t="s" s="2">
+        <v>870</v>
+      </c>
       <c r="P497" t="s" s="2">
         <v>78</v>
       </c>
@@ -62633,38 +62648,40 @@
         <v>78</v>
       </c>
       <c r="X497" t="s" s="2">
-        <v>78</v>
+        <v>175</v>
       </c>
       <c r="Y497" t="s" s="2">
-        <v>78</v>
+        <v>871</v>
       </c>
       <c r="Z497" t="s" s="2">
-        <v>78</v>
+        <v>872</v>
       </c>
       <c r="AA497" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AB497" t="s" s="2">
-        <v>915</v>
-      </c>
-      <c r="AC497" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="AC497" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="AD497" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE497" t="s" s="2">
-        <v>118</v>
+        <v>78</v>
       </c>
       <c r="AF497" t="s" s="2">
-        <v>874</v>
+        <v>866</v>
       </c>
       <c r="AG497" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH497" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI497" t="s" s="2">
-        <v>878</v>
+        <v>78</v>
       </c>
       <c r="AJ497" t="s" s="2">
         <v>103</v>
@@ -62673,10 +62690,10 @@
         <v>78</v>
       </c>
       <c r="AL497" t="s" s="2">
-        <v>879</v>
+        <v>873</v>
       </c>
       <c r="AM497" t="s" s="2">
-        <v>880</v>
+        <v>109</v>
       </c>
       <c r="AN497" t="s" s="2">
         <v>78</v>
@@ -62687,14 +62704,12 @@
     </row>
     <row r="498" hidden="true">
       <c r="A498" t="s" s="2">
-        <v>1251</v>
+        <v>1254</v>
       </c>
       <c r="B498" t="s" s="2">
         <v>874</v>
       </c>
-      <c r="C498" t="s" s="2">
-        <v>1252</v>
-      </c>
+      <c r="C498" s="2"/>
       <c r="D498" t="s" s="2">
         <v>78</v>
       </c>
@@ -62715,10 +62730,10 @@
         <v>78</v>
       </c>
       <c r="K498" t="s" s="2">
-        <v>1253</v>
+        <v>797</v>
       </c>
       <c r="L498" t="s" s="2">
-        <v>1254</v>
+        <v>875</v>
       </c>
       <c r="M498" t="s" s="2">
         <v>876</v>
@@ -62762,16 +62777,14 @@
         <v>78</v>
       </c>
       <c r="AB498" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC498" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>915</v>
+      </c>
+      <c r="AC498" s="2"/>
       <c r="AD498" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE498" t="s" s="2">
-        <v>78</v>
+        <v>118</v>
       </c>
       <c r="AF498" t="s" s="2">
         <v>874</v>
@@ -63042,14 +63055,16 @@
         <v>78</v>
       </c>
     </row>
-    <row r="501">
+    <row r="501" hidden="true">
       <c r="A501" t="s" s="2">
         <v>1263</v>
       </c>
       <c r="B501" t="s" s="2">
-        <v>881</v>
-      </c>
-      <c r="C501" s="2"/>
+        <v>874</v>
+      </c>
+      <c r="C501" t="s" s="2">
+        <v>1264</v>
+      </c>
       <c r="D501" t="s" s="2">
         <v>78</v>
       </c>
@@ -63058,10 +63073,10 @@
         <v>79</v>
       </c>
       <c r="G501" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H501" t="s" s="2">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="I501" t="s" s="2">
         <v>78</v>
@@ -63070,20 +63085,18 @@
         <v>78</v>
       </c>
       <c r="K501" t="s" s="2">
-        <v>235</v>
+        <v>1265</v>
       </c>
       <c r="L501" t="s" s="2">
-        <v>921</v>
+        <v>1266</v>
       </c>
       <c r="M501" t="s" s="2">
-        <v>883</v>
+        <v>876</v>
       </c>
       <c r="N501" t="s" s="2">
-        <v>884</v>
-      </c>
-      <c r="O501" t="s" s="2">
-        <v>885</v>
-      </c>
+        <v>877</v>
+      </c>
+      <c r="O501" s="2"/>
       <c r="P501" t="s" s="2">
         <v>78</v>
       </c>
@@ -63107,11 +63120,13 @@
         <v>78</v>
       </c>
       <c r="X501" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="Y501" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y501" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z501" t="s" s="2">
-        <v>887</v>
+        <v>78</v>
       </c>
       <c r="AA501" t="s" s="2">
         <v>78</v>
@@ -63129,13 +63144,13 @@
         <v>78</v>
       </c>
       <c r="AF501" t="s" s="2">
-        <v>881</v>
+        <v>874</v>
       </c>
       <c r="AG501" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH501" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI501" t="s" s="2">
         <v>878</v>
@@ -63147,10 +63162,10 @@
         <v>78</v>
       </c>
       <c r="AL501" t="s" s="2">
-        <v>888</v>
+        <v>879</v>
       </c>
       <c r="AM501" t="s" s="2">
-        <v>109</v>
+        <v>880</v>
       </c>
       <c r="AN501" t="s" s="2">
         <v>78</v>
@@ -63159,12 +63174,12 @@
         <v>78</v>
       </c>
     </row>
-    <row r="502" hidden="true">
+    <row r="502">
       <c r="A502" t="s" s="2">
-        <v>1264</v>
+        <v>1267</v>
       </c>
       <c r="B502" t="s" s="2">
-        <v>889</v>
+        <v>881</v>
       </c>
       <c r="C502" s="2"/>
       <c r="D502" t="s" s="2">
@@ -63175,10 +63190,10 @@
         <v>79</v>
       </c>
       <c r="G502" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H502" t="s" s="2">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="I502" t="s" s="2">
         <v>78</v>
@@ -63187,18 +63202,20 @@
         <v>78</v>
       </c>
       <c r="K502" t="s" s="2">
-        <v>81</v>
+        <v>235</v>
       </c>
       <c r="L502" t="s" s="2">
-        <v>890</v>
+        <v>921</v>
       </c>
       <c r="M502" t="s" s="2">
-        <v>891</v>
+        <v>883</v>
       </c>
       <c r="N502" t="s" s="2">
-        <v>892</v>
-      </c>
-      <c r="O502" s="2"/>
+        <v>884</v>
+      </c>
+      <c r="O502" t="s" s="2">
+        <v>885</v>
+      </c>
       <c r="P502" t="s" s="2">
         <v>78</v>
       </c>
@@ -63222,13 +63239,11 @@
         <v>78</v>
       </c>
       <c r="X502" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y502" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>175</v>
+      </c>
+      <c r="Y502" s="2"/>
       <c r="Z502" t="s" s="2">
-        <v>78</v>
+        <v>887</v>
       </c>
       <c r="AA502" t="s" s="2">
         <v>78</v>
@@ -63246,16 +63261,16 @@
         <v>78</v>
       </c>
       <c r="AF502" t="s" s="2">
-        <v>889</v>
+        <v>881</v>
       </c>
       <c r="AG502" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH502" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI502" t="s" s="2">
-        <v>856</v>
+        <v>878</v>
       </c>
       <c r="AJ502" t="s" s="2">
         <v>103</v>
@@ -63264,10 +63279,10 @@
         <v>78</v>
       </c>
       <c r="AL502" t="s" s="2">
-        <v>818</v>
+        <v>888</v>
       </c>
       <c r="AM502" t="s" s="2">
-        <v>893</v>
+        <v>109</v>
       </c>
       <c r="AN502" t="s" s="2">
         <v>78</v>
@@ -63276,16 +63291,14 @@
         <v>78</v>
       </c>
     </row>
-    <row r="503">
+    <row r="503" hidden="true">
       <c r="A503" t="s" s="2">
-        <v>1265</v>
+        <v>1268</v>
       </c>
       <c r="B503" t="s" s="2">
-        <v>812</v>
-      </c>
-      <c r="C503" t="s" s="2">
-        <v>1266</v>
-      </c>
+        <v>889</v>
+      </c>
+      <c r="C503" s="2"/>
       <c r="D503" t="s" s="2">
         <v>78</v>
       </c>
@@ -63294,10 +63307,10 @@
         <v>79</v>
       </c>
       <c r="G503" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H503" t="s" s="2">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="I503" t="s" s="2">
         <v>78</v>
@@ -63306,15 +63319,17 @@
         <v>78</v>
       </c>
       <c r="K503" t="s" s="2">
-        <v>568</v>
+        <v>81</v>
       </c>
       <c r="L503" t="s" s="2">
-        <v>1267</v>
+        <v>890</v>
       </c>
       <c r="M503" t="s" s="2">
-        <v>1268</v>
-      </c>
-      <c r="N503" s="2"/>
+        <v>891</v>
+      </c>
+      <c r="N503" t="s" s="2">
+        <v>892</v>
+      </c>
       <c r="O503" s="2"/>
       <c r="P503" t="s" s="2">
         <v>78</v>
@@ -63363,7 +63378,7 @@
         <v>78</v>
       </c>
       <c r="AF503" t="s" s="2">
-        <v>812</v>
+        <v>889</v>
       </c>
       <c r="AG503" t="s" s="2">
         <v>79</v>
@@ -63372,10 +63387,10 @@
         <v>80</v>
       </c>
       <c r="AI503" t="s" s="2">
-        <v>78</v>
+        <v>856</v>
       </c>
       <c r="AJ503" t="s" s="2">
-        <v>817</v>
+        <v>103</v>
       </c>
       <c r="AK503" t="s" s="2">
         <v>78</v>
@@ -63384,7 +63399,7 @@
         <v>818</v>
       </c>
       <c r="AM503" t="s" s="2">
-        <v>819</v>
+        <v>893</v>
       </c>
       <c r="AN503" t="s" s="2">
         <v>78</v>
@@ -63393,14 +63408,16 @@
         <v>78</v>
       </c>
     </row>
-    <row r="504" hidden="true">
+    <row r="504">
       <c r="A504" t="s" s="2">
         <v>1269</v>
       </c>
       <c r="B504" t="s" s="2">
-        <v>820</v>
-      </c>
-      <c r="C504" s="2"/>
+        <v>812</v>
+      </c>
+      <c r="C504" t="s" s="2">
+        <v>1270</v>
+      </c>
       <c r="D504" t="s" s="2">
         <v>78</v>
       </c>
@@ -63412,7 +63429,7 @@
         <v>91</v>
       </c>
       <c r="H504" t="s" s="2">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="I504" t="s" s="2">
         <v>78</v>
@@ -63421,13 +63438,13 @@
         <v>78</v>
       </c>
       <c r="K504" t="s" s="2">
-        <v>105</v>
+        <v>568</v>
       </c>
       <c r="L504" t="s" s="2">
-        <v>106</v>
+        <v>1271</v>
       </c>
       <c r="M504" t="s" s="2">
-        <v>107</v>
+        <v>1272</v>
       </c>
       <c r="N504" s="2"/>
       <c r="O504" s="2"/>
@@ -63478,28 +63495,28 @@
         <v>78</v>
       </c>
       <c r="AF504" t="s" s="2">
-        <v>108</v>
+        <v>812</v>
       </c>
       <c r="AG504" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH504" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI504" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ504" t="s" s="2">
-        <v>78</v>
+        <v>817</v>
       </c>
       <c r="AK504" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL504" t="s" s="2">
-        <v>109</v>
+        <v>818</v>
       </c>
       <c r="AM504" t="s" s="2">
-        <v>78</v>
+        <v>819</v>
       </c>
       <c r="AN504" t="s" s="2">
         <v>78</v>
@@ -63510,10 +63527,10 @@
     </row>
     <row r="505" hidden="true">
       <c r="A505" t="s" s="2">
-        <v>1270</v>
+        <v>1273</v>
       </c>
       <c r="B505" t="s" s="2">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="C505" s="2"/>
       <c r="D505" t="s" s="2">
@@ -63524,7 +63541,7 @@
         <v>79</v>
       </c>
       <c r="G505" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H505" t="s" s="2">
         <v>78</v>
@@ -63536,13 +63553,13 @@
         <v>78</v>
       </c>
       <c r="K505" t="s" s="2">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="L505" t="s" s="2">
-        <v>197</v>
+        <v>106</v>
       </c>
       <c r="M505" t="s" s="2">
-        <v>198</v>
+        <v>107</v>
       </c>
       <c r="N505" s="2"/>
       <c r="O505" s="2"/>
@@ -63581,35 +63598,37 @@
         <v>78</v>
       </c>
       <c r="AB505" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="AC505" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="AC505" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="AD505" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE505" t="s" s="2">
-        <v>118</v>
+        <v>78</v>
       </c>
       <c r="AF505" t="s" s="2">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="AG505" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH505" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI505" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ505" t="s" s="2">
-        <v>120</v>
+        <v>78</v>
       </c>
       <c r="AK505" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL505" t="s" s="2">
-        <v>78</v>
+        <v>109</v>
       </c>
       <c r="AM505" t="s" s="2">
         <v>78</v>
@@ -63623,14 +63642,12 @@
     </row>
     <row r="506" hidden="true">
       <c r="A506" t="s" s="2">
-        <v>1271</v>
+        <v>1274</v>
       </c>
       <c r="B506" t="s" s="2">
         <v>821</v>
       </c>
-      <c r="C506" t="s" s="2">
-        <v>405</v>
-      </c>
+      <c r="C506" s="2"/>
       <c r="D506" t="s" s="2">
         <v>78</v>
       </c>
@@ -63639,7 +63656,7 @@
         <v>79</v>
       </c>
       <c r="G506" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H506" t="s" s="2">
         <v>78</v>
@@ -63651,13 +63668,13 @@
         <v>78</v>
       </c>
       <c r="K506" t="s" s="2">
-        <v>407</v>
+        <v>112</v>
       </c>
       <c r="L506" t="s" s="2">
-        <v>823</v>
+        <v>197</v>
       </c>
       <c r="M506" t="s" s="2">
-        <v>408</v>
+        <v>198</v>
       </c>
       <c r="N506" s="2"/>
       <c r="O506" s="2"/>
@@ -63696,16 +63713,14 @@
         <v>78</v>
       </c>
       <c r="AB506" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC506" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>116</v>
+      </c>
+      <c r="AC506" s="2"/>
       <c r="AD506" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE506" t="s" s="2">
-        <v>78</v>
+        <v>118</v>
       </c>
       <c r="AF506" t="s" s="2">
         <v>119</v>
@@ -63717,7 +63732,7 @@
         <v>80</v>
       </c>
       <c r="AI506" t="s" s="2">
-        <v>207</v>
+        <v>78</v>
       </c>
       <c r="AJ506" t="s" s="2">
         <v>120</v>
@@ -63740,13 +63755,13 @@
     </row>
     <row r="507" hidden="true">
       <c r="A507" t="s" s="2">
-        <v>1272</v>
+        <v>1275</v>
       </c>
       <c r="B507" t="s" s="2">
         <v>821</v>
       </c>
       <c r="C507" t="s" s="2">
-        <v>825</v>
+        <v>405</v>
       </c>
       <c r="D507" t="s" s="2">
         <v>78</v>
@@ -63756,7 +63771,7 @@
         <v>79</v>
       </c>
       <c r="G507" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H507" t="s" s="2">
         <v>78</v>
@@ -63768,17 +63783,15 @@
         <v>78</v>
       </c>
       <c r="K507" t="s" s="2">
-        <v>826</v>
+        <v>407</v>
       </c>
       <c r="L507" t="s" s="2">
-        <v>827</v>
+        <v>823</v>
       </c>
       <c r="M507" t="s" s="2">
-        <v>828</v>
-      </c>
-      <c r="N507" t="s" s="2">
-        <v>829</v>
-      </c>
+        <v>408</v>
+      </c>
+      <c r="N507" s="2"/>
       <c r="O507" s="2"/>
       <c r="P507" t="s" s="2">
         <v>78</v>
@@ -63836,7 +63849,7 @@
         <v>80</v>
       </c>
       <c r="AI507" t="s" s="2">
-        <v>78</v>
+        <v>207</v>
       </c>
       <c r="AJ507" t="s" s="2">
         <v>120</v>
@@ -63859,14 +63872,16 @@
     </row>
     <row r="508" hidden="true">
       <c r="A508" t="s" s="2">
-        <v>1273</v>
+        <v>1276</v>
       </c>
       <c r="B508" t="s" s="2">
-        <v>830</v>
-      </c>
-      <c r="C508" s="2"/>
+        <v>821</v>
+      </c>
+      <c r="C508" t="s" s="2">
+        <v>825</v>
+      </c>
       <c r="D508" t="s" s="2">
-        <v>581</v>
+        <v>78</v>
       </c>
       <c r="E508" s="2"/>
       <c r="F508" t="s" s="2">
@@ -63879,26 +63894,24 @@
         <v>78</v>
       </c>
       <c r="I508" t="s" s="2">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="J508" t="s" s="2">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="K508" t="s" s="2">
-        <v>112</v>
+        <v>826</v>
       </c>
       <c r="L508" t="s" s="2">
-        <v>582</v>
+        <v>827</v>
       </c>
       <c r="M508" t="s" s="2">
-        <v>583</v>
+        <v>828</v>
       </c>
       <c r="N508" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="O508" t="s" s="2">
-        <v>412</v>
-      </c>
+        <v>829</v>
+      </c>
+      <c r="O508" s="2"/>
       <c r="P508" t="s" s="2">
         <v>78</v>
       </c>
@@ -63946,7 +63959,7 @@
         <v>78</v>
       </c>
       <c r="AF508" t="s" s="2">
-        <v>584</v>
+        <v>119</v>
       </c>
       <c r="AG508" t="s" s="2">
         <v>79</v>
@@ -63964,7 +63977,7 @@
         <v>78</v>
       </c>
       <c r="AL508" t="s" s="2">
-        <v>195</v>
+        <v>78</v>
       </c>
       <c r="AM508" t="s" s="2">
         <v>78</v>
@@ -63976,47 +63989,47 @@
         <v>78</v>
       </c>
     </row>
-    <row r="509">
+    <row r="509" hidden="true">
       <c r="A509" t="s" s="2">
-        <v>1274</v>
+        <v>1277</v>
       </c>
       <c r="B509" t="s" s="2">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="C509" s="2"/>
       <c r="D509" t="s" s="2">
-        <v>832</v>
+        <v>581</v>
       </c>
       <c r="E509" s="2"/>
       <c r="F509" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="G509" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H509" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I509" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="I509" t="s" s="2">
-        <v>78</v>
-      </c>
       <c r="J509" t="s" s="2">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="K509" t="s" s="2">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="L509" t="s" s="2">
-        <v>1275</v>
+        <v>582</v>
       </c>
       <c r="M509" t="s" s="2">
-        <v>834</v>
+        <v>583</v>
       </c>
       <c r="N509" t="s" s="2">
-        <v>835</v>
+        <v>115</v>
       </c>
       <c r="O509" t="s" s="2">
-        <v>836</v>
+        <v>412</v>
       </c>
       <c r="P509" t="s" s="2">
         <v>78</v>
@@ -64065,28 +64078,28 @@
         <v>78</v>
       </c>
       <c r="AF509" t="s" s="2">
-        <v>831</v>
+        <v>584</v>
       </c>
       <c r="AG509" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH509" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI509" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ509" t="s" s="2">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="AK509" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL509" t="s" s="2">
-        <v>556</v>
+        <v>195</v>
       </c>
       <c r="AM509" t="s" s="2">
-        <v>557</v>
+        <v>78</v>
       </c>
       <c r="AN509" t="s" s="2">
         <v>78</v>
@@ -64097,14 +64110,14 @@
     </row>
     <row r="510">
       <c r="A510" t="s" s="2">
-        <v>1276</v>
+        <v>1278</v>
       </c>
       <c r="B510" t="s" s="2">
-        <v>837</v>
+        <v>831</v>
       </c>
       <c r="C510" s="2"/>
       <c r="D510" t="s" s="2">
-        <v>78</v>
+        <v>832</v>
       </c>
       <c r="E510" s="2"/>
       <c r="F510" t="s" s="2">
@@ -64123,19 +64136,19 @@
         <v>78</v>
       </c>
       <c r="K510" t="s" s="2">
-        <v>235</v>
+        <v>105</v>
       </c>
       <c r="L510" t="s" s="2">
-        <v>838</v>
+        <v>1279</v>
       </c>
       <c r="M510" t="s" s="2">
-        <v>839</v>
+        <v>834</v>
       </c>
       <c r="N510" t="s" s="2">
-        <v>840</v>
+        <v>835</v>
       </c>
       <c r="O510" t="s" s="2">
-        <v>841</v>
+        <v>836</v>
       </c>
       <c r="P510" t="s" s="2">
         <v>78</v>
@@ -64145,7 +64158,7 @@
         <v>78</v>
       </c>
       <c r="S510" t="s" s="2">
-        <v>1277</v>
+        <v>78</v>
       </c>
       <c r="T510" t="s" s="2">
         <v>78</v>
@@ -64160,11 +64173,13 @@
         <v>78</v>
       </c>
       <c r="X510" t="s" s="2">
-        <v>325</v>
-      </c>
-      <c r="Y510" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y510" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z510" t="s" s="2">
-        <v>842</v>
+        <v>78</v>
       </c>
       <c r="AA510" t="s" s="2">
         <v>78</v>
@@ -64182,7 +64197,7 @@
         <v>78</v>
       </c>
       <c r="AF510" t="s" s="2">
-        <v>837</v>
+        <v>831</v>
       </c>
       <c r="AG510" t="s" s="2">
         <v>79</v>
@@ -64200,10 +64215,10 @@
         <v>78</v>
       </c>
       <c r="AL510" t="s" s="2">
-        <v>457</v>
+        <v>556</v>
       </c>
       <c r="AM510" t="s" s="2">
-        <v>458</v>
+        <v>557</v>
       </c>
       <c r="AN510" t="s" s="2">
         <v>78</v>
@@ -64212,12 +64227,12 @@
         <v>78</v>
       </c>
     </row>
-    <row r="511" hidden="true">
+    <row r="511">
       <c r="A511" t="s" s="2">
-        <v>1278</v>
+        <v>1280</v>
       </c>
       <c r="B511" t="s" s="2">
-        <v>843</v>
+        <v>837</v>
       </c>
       <c r="C511" s="2"/>
       <c r="D511" t="s" s="2">
@@ -64225,13 +64240,13 @@
       </c>
       <c r="E511" s="2"/>
       <c r="F511" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="G511" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H511" t="s" s="2">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="I511" t="s" s="2">
         <v>78</v>
@@ -64240,17 +64255,19 @@
         <v>78</v>
       </c>
       <c r="K511" t="s" s="2">
-        <v>844</v>
+        <v>235</v>
       </c>
       <c r="L511" t="s" s="2">
-        <v>845</v>
+        <v>838</v>
       </c>
       <c r="M511" t="s" s="2">
-        <v>846</v>
-      </c>
-      <c r="N511" s="2"/>
+        <v>839</v>
+      </c>
+      <c r="N511" t="s" s="2">
+        <v>840</v>
+      </c>
       <c r="O511" t="s" s="2">
-        <v>536</v>
+        <v>841</v>
       </c>
       <c r="P511" t="s" s="2">
         <v>78</v>
@@ -64260,7 +64277,7 @@
         <v>78</v>
       </c>
       <c r="S511" t="s" s="2">
-        <v>78</v>
+        <v>1281</v>
       </c>
       <c r="T511" t="s" s="2">
         <v>78</v>
@@ -64275,13 +64292,11 @@
         <v>78</v>
       </c>
       <c r="X511" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y511" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>325</v>
+      </c>
+      <c r="Y511" s="2"/>
       <c r="Z511" t="s" s="2">
-        <v>78</v>
+        <v>842</v>
       </c>
       <c r="AA511" t="s" s="2">
         <v>78</v>
@@ -64299,13 +64314,13 @@
         <v>78</v>
       </c>
       <c r="AF511" t="s" s="2">
-        <v>843</v>
+        <v>837</v>
       </c>
       <c r="AG511" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH511" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI511" t="s" s="2">
         <v>78</v>
@@ -64317,24 +64332,24 @@
         <v>78</v>
       </c>
       <c r="AL511" t="s" s="2">
-        <v>538</v>
+        <v>457</v>
       </c>
       <c r="AM511" t="s" s="2">
-        <v>539</v>
+        <v>458</v>
       </c>
       <c r="AN511" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO511" t="s" s="2">
-        <v>541</v>
+        <v>78</v>
       </c>
     </row>
     <row r="512" hidden="true">
       <c r="A512" t="s" s="2">
-        <v>1279</v>
+        <v>1282</v>
       </c>
       <c r="B512" t="s" s="2">
-        <v>847</v>
+        <v>843</v>
       </c>
       <c r="C512" s="2"/>
       <c r="D512" t="s" s="2">
@@ -64345,7 +64360,7 @@
         <v>79</v>
       </c>
       <c r="G512" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H512" t="s" s="2">
         <v>78</v>
@@ -64357,18 +64372,18 @@
         <v>78</v>
       </c>
       <c r="K512" t="s" s="2">
-        <v>797</v>
+        <v>844</v>
       </c>
       <c r="L512" t="s" s="2">
-        <v>848</v>
+        <v>845</v>
       </c>
       <c r="M512" t="s" s="2">
-        <v>849</v>
-      </c>
-      <c r="N512" t="s" s="2">
-        <v>850</v>
-      </c>
-      <c r="O512" s="2"/>
+        <v>846</v>
+      </c>
+      <c r="N512" s="2"/>
+      <c r="O512" t="s" s="2">
+        <v>536</v>
+      </c>
       <c r="P512" t="s" s="2">
         <v>78</v>
       </c>
@@ -64416,13 +64431,13 @@
         <v>78</v>
       </c>
       <c r="AF512" t="s" s="2">
-        <v>847</v>
+        <v>843</v>
       </c>
       <c r="AG512" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH512" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI512" t="s" s="2">
         <v>78</v>
@@ -64434,24 +64449,24 @@
         <v>78</v>
       </c>
       <c r="AL512" t="s" s="2">
-        <v>78</v>
+        <v>538</v>
       </c>
       <c r="AM512" t="s" s="2">
-        <v>851</v>
+        <v>539</v>
       </c>
       <c r="AN512" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO512" t="s" s="2">
-        <v>78</v>
+        <v>541</v>
       </c>
     </row>
-    <row r="513">
+    <row r="513" hidden="true">
       <c r="A513" t="s" s="2">
-        <v>1280</v>
+        <v>1283</v>
       </c>
       <c r="B513" t="s" s="2">
-        <v>852</v>
+        <v>847</v>
       </c>
       <c r="C513" s="2"/>
       <c r="D513" t="s" s="2">
@@ -64459,13 +64474,13 @@
       </c>
       <c r="E513" s="2"/>
       <c r="F513" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="G513" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H513" t="s" s="2">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="I513" t="s" s="2">
         <v>78</v>
@@ -64474,16 +64489,16 @@
         <v>78</v>
       </c>
       <c r="K513" t="s" s="2">
-        <v>182</v>
+        <v>797</v>
       </c>
       <c r="L513" t="s" s="2">
-        <v>1281</v>
+        <v>848</v>
       </c>
       <c r="M513" t="s" s="2">
-        <v>854</v>
+        <v>849</v>
       </c>
       <c r="N513" t="s" s="2">
-        <v>855</v>
+        <v>850</v>
       </c>
       <c r="O513" s="2"/>
       <c r="P513" t="s" s="2">
@@ -64533,7 +64548,7 @@
         <v>78</v>
       </c>
       <c r="AF513" t="s" s="2">
-        <v>852</v>
+        <v>847</v>
       </c>
       <c r="AG513" t="s" s="2">
         <v>79</v>
@@ -64542,7 +64557,7 @@
         <v>91</v>
       </c>
       <c r="AI513" t="s" s="2">
-        <v>856</v>
+        <v>78</v>
       </c>
       <c r="AJ513" t="s" s="2">
         <v>103</v>
@@ -64551,10 +64566,10 @@
         <v>78</v>
       </c>
       <c r="AL513" t="s" s="2">
-        <v>857</v>
+        <v>78</v>
       </c>
       <c r="AM513" t="s" s="2">
-        <v>857</v>
+        <v>851</v>
       </c>
       <c r="AN513" t="s" s="2">
         <v>78</v>
@@ -64563,12 +64578,12 @@
         <v>78</v>
       </c>
     </row>
-    <row r="514" hidden="true">
+    <row r="514">
       <c r="A514" t="s" s="2">
-        <v>1282</v>
+        <v>1284</v>
       </c>
       <c r="B514" t="s" s="2">
-        <v>858</v>
+        <v>852</v>
       </c>
       <c r="C514" s="2"/>
       <c r="D514" t="s" s="2">
@@ -64576,13 +64591,13 @@
       </c>
       <c r="E514" s="2"/>
       <c r="F514" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="G514" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H514" t="s" s="2">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="I514" t="s" s="2">
         <v>78</v>
@@ -64591,20 +64606,18 @@
         <v>78</v>
       </c>
       <c r="K514" t="s" s="2">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="L514" t="s" s="2">
-        <v>859</v>
+        <v>1285</v>
       </c>
       <c r="M514" t="s" s="2">
-        <v>860</v>
+        <v>854</v>
       </c>
       <c r="N514" t="s" s="2">
-        <v>861</v>
-      </c>
-      <c r="O514" t="s" s="2">
-        <v>862</v>
-      </c>
+        <v>855</v>
+      </c>
+      <c r="O514" s="2"/>
       <c r="P514" t="s" s="2">
         <v>78</v>
       </c>
@@ -64628,13 +64641,13 @@
         <v>78</v>
       </c>
       <c r="X514" t="s" s="2">
-        <v>325</v>
+        <v>78</v>
       </c>
       <c r="Y514" t="s" s="2">
-        <v>863</v>
+        <v>78</v>
       </c>
       <c r="Z514" t="s" s="2">
-        <v>864</v>
+        <v>78</v>
       </c>
       <c r="AA514" t="s" s="2">
         <v>78</v>
@@ -64652,7 +64665,7 @@
         <v>78</v>
       </c>
       <c r="AF514" t="s" s="2">
-        <v>858</v>
+        <v>852</v>
       </c>
       <c r="AG514" t="s" s="2">
         <v>79</v>
@@ -64661,7 +64674,7 @@
         <v>91</v>
       </c>
       <c r="AI514" t="s" s="2">
-        <v>78</v>
+        <v>856</v>
       </c>
       <c r="AJ514" t="s" s="2">
         <v>103</v>
@@ -64670,24 +64683,24 @@
         <v>78</v>
       </c>
       <c r="AL514" t="s" s="2">
-        <v>865</v>
+        <v>857</v>
       </c>
       <c r="AM514" t="s" s="2">
-        <v>109</v>
+        <v>857</v>
       </c>
       <c r="AN514" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO514" t="s" s="2">
-        <v>460</v>
+        <v>78</v>
       </c>
     </row>
     <row r="515" hidden="true">
       <c r="A515" t="s" s="2">
-        <v>1283</v>
+        <v>1286</v>
       </c>
       <c r="B515" t="s" s="2">
-        <v>866</v>
+        <v>858</v>
       </c>
       <c r="C515" s="2"/>
       <c r="D515" t="s" s="2">
@@ -64710,19 +64723,19 @@
         <v>78</v>
       </c>
       <c r="K515" t="s" s="2">
-        <v>235</v>
+        <v>171</v>
       </c>
       <c r="L515" t="s" s="2">
-        <v>867</v>
+        <v>859</v>
       </c>
       <c r="M515" t="s" s="2">
-        <v>868</v>
+        <v>860</v>
       </c>
       <c r="N515" t="s" s="2">
-        <v>869</v>
+        <v>861</v>
       </c>
       <c r="O515" t="s" s="2">
-        <v>870</v>
+        <v>862</v>
       </c>
       <c r="P515" t="s" s="2">
         <v>78</v>
@@ -64747,13 +64760,13 @@
         <v>78</v>
       </c>
       <c r="X515" t="s" s="2">
-        <v>175</v>
+        <v>325</v>
       </c>
       <c r="Y515" t="s" s="2">
-        <v>871</v>
+        <v>863</v>
       </c>
       <c r="Z515" t="s" s="2">
-        <v>872</v>
+        <v>864</v>
       </c>
       <c r="AA515" t="s" s="2">
         <v>78</v>
@@ -64771,7 +64784,7 @@
         <v>78</v>
       </c>
       <c r="AF515" t="s" s="2">
-        <v>866</v>
+        <v>858</v>
       </c>
       <c r="AG515" t="s" s="2">
         <v>79</v>
@@ -64789,7 +64802,7 @@
         <v>78</v>
       </c>
       <c r="AL515" t="s" s="2">
-        <v>873</v>
+        <v>865</v>
       </c>
       <c r="AM515" t="s" s="2">
         <v>109</v>
@@ -64798,15 +64811,15 @@
         <v>78</v>
       </c>
       <c r="AO515" t="s" s="2">
-        <v>78</v>
+        <v>460</v>
       </c>
     </row>
     <row r="516" hidden="true">
       <c r="A516" t="s" s="2">
-        <v>1284</v>
+        <v>1287</v>
       </c>
       <c r="B516" t="s" s="2">
-        <v>874</v>
+        <v>866</v>
       </c>
       <c r="C516" s="2"/>
       <c r="D516" t="s" s="2">
@@ -64817,7 +64830,7 @@
         <v>79</v>
       </c>
       <c r="G516" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H516" t="s" s="2">
         <v>78</v>
@@ -64829,18 +64842,20 @@
         <v>78</v>
       </c>
       <c r="K516" t="s" s="2">
-        <v>797</v>
+        <v>235</v>
       </c>
       <c r="L516" t="s" s="2">
-        <v>875</v>
+        <v>867</v>
       </c>
       <c r="M516" t="s" s="2">
-        <v>876</v>
+        <v>868</v>
       </c>
       <c r="N516" t="s" s="2">
-        <v>877</v>
-      </c>
-      <c r="O516" s="2"/>
+        <v>869</v>
+      </c>
+      <c r="O516" t="s" s="2">
+        <v>870</v>
+      </c>
       <c r="P516" t="s" s="2">
         <v>78</v>
       </c>
@@ -64864,38 +64879,40 @@
         <v>78</v>
       </c>
       <c r="X516" t="s" s="2">
-        <v>78</v>
+        <v>175</v>
       </c>
       <c r="Y516" t="s" s="2">
-        <v>78</v>
+        <v>871</v>
       </c>
       <c r="Z516" t="s" s="2">
-        <v>78</v>
+        <v>872</v>
       </c>
       <c r="AA516" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AB516" t="s" s="2">
-        <v>915</v>
-      </c>
-      <c r="AC516" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="AC516" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="AD516" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE516" t="s" s="2">
-        <v>118</v>
+        <v>78</v>
       </c>
       <c r="AF516" t="s" s="2">
-        <v>874</v>
+        <v>866</v>
       </c>
       <c r="AG516" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH516" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI516" t="s" s="2">
-        <v>878</v>
+        <v>78</v>
       </c>
       <c r="AJ516" t="s" s="2">
         <v>103</v>
@@ -64904,10 +64921,10 @@
         <v>78</v>
       </c>
       <c r="AL516" t="s" s="2">
-        <v>879</v>
+        <v>873</v>
       </c>
       <c r="AM516" t="s" s="2">
-        <v>880</v>
+        <v>109</v>
       </c>
       <c r="AN516" t="s" s="2">
         <v>78</v>
@@ -64918,14 +64935,12 @@
     </row>
     <row r="517" hidden="true">
       <c r="A517" t="s" s="2">
-        <v>1285</v>
+        <v>1288</v>
       </c>
       <c r="B517" t="s" s="2">
         <v>874</v>
       </c>
-      <c r="C517" t="s" s="2">
-        <v>1286</v>
-      </c>
+      <c r="C517" s="2"/>
       <c r="D517" t="s" s="2">
         <v>78</v>
       </c>
@@ -64946,10 +64961,10 @@
         <v>78</v>
       </c>
       <c r="K517" t="s" s="2">
-        <v>1287</v>
+        <v>797</v>
       </c>
       <c r="L517" t="s" s="2">
-        <v>1288</v>
+        <v>875</v>
       </c>
       <c r="M517" t="s" s="2">
         <v>876</v>
@@ -64993,16 +65008,14 @@
         <v>78</v>
       </c>
       <c r="AB517" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC517" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>915</v>
+      </c>
+      <c r="AC517" s="2"/>
       <c r="AD517" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE517" t="s" s="2">
-        <v>78</v>
+        <v>118</v>
       </c>
       <c r="AF517" t="s" s="2">
         <v>874</v>
@@ -65035,14 +65048,16 @@
         <v>78</v>
       </c>
     </row>
-    <row r="518">
+    <row r="518" hidden="true">
       <c r="A518" t="s" s="2">
         <v>1289</v>
       </c>
       <c r="B518" t="s" s="2">
-        <v>881</v>
-      </c>
-      <c r="C518" s="2"/>
+        <v>874</v>
+      </c>
+      <c r="C518" t="s" s="2">
+        <v>1290</v>
+      </c>
       <c r="D518" t="s" s="2">
         <v>78</v>
       </c>
@@ -65051,10 +65066,10 @@
         <v>79</v>
       </c>
       <c r="G518" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H518" t="s" s="2">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="I518" t="s" s="2">
         <v>78</v>
@@ -65063,20 +65078,18 @@
         <v>78</v>
       </c>
       <c r="K518" t="s" s="2">
-        <v>235</v>
+        <v>1291</v>
       </c>
       <c r="L518" t="s" s="2">
-        <v>921</v>
+        <v>1292</v>
       </c>
       <c r="M518" t="s" s="2">
-        <v>883</v>
+        <v>876</v>
       </c>
       <c r="N518" t="s" s="2">
-        <v>884</v>
-      </c>
-      <c r="O518" t="s" s="2">
-        <v>885</v>
-      </c>
+        <v>877</v>
+      </c>
+      <c r="O518" s="2"/>
       <c r="P518" t="s" s="2">
         <v>78</v>
       </c>
@@ -65100,11 +65113,13 @@
         <v>78</v>
       </c>
       <c r="X518" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="Y518" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y518" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z518" t="s" s="2">
-        <v>887</v>
+        <v>78</v>
       </c>
       <c r="AA518" t="s" s="2">
         <v>78</v>
@@ -65122,13 +65137,13 @@
         <v>78</v>
       </c>
       <c r="AF518" t="s" s="2">
-        <v>881</v>
+        <v>874</v>
       </c>
       <c r="AG518" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH518" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI518" t="s" s="2">
         <v>878</v>
@@ -65140,10 +65155,10 @@
         <v>78</v>
       </c>
       <c r="AL518" t="s" s="2">
-        <v>888</v>
+        <v>879</v>
       </c>
       <c r="AM518" t="s" s="2">
-        <v>109</v>
+        <v>880</v>
       </c>
       <c r="AN518" t="s" s="2">
         <v>78</v>
@@ -65152,12 +65167,12 @@
         <v>78</v>
       </c>
     </row>
-    <row r="519" hidden="true">
+    <row r="519">
       <c r="A519" t="s" s="2">
-        <v>1290</v>
+        <v>1293</v>
       </c>
       <c r="B519" t="s" s="2">
-        <v>889</v>
+        <v>881</v>
       </c>
       <c r="C519" s="2"/>
       <c r="D519" t="s" s="2">
@@ -65168,10 +65183,10 @@
         <v>79</v>
       </c>
       <c r="G519" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H519" t="s" s="2">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="I519" t="s" s="2">
         <v>78</v>
@@ -65180,18 +65195,20 @@
         <v>78</v>
       </c>
       <c r="K519" t="s" s="2">
-        <v>81</v>
+        <v>235</v>
       </c>
       <c r="L519" t="s" s="2">
-        <v>890</v>
+        <v>921</v>
       </c>
       <c r="M519" t="s" s="2">
-        <v>891</v>
+        <v>883</v>
       </c>
       <c r="N519" t="s" s="2">
-        <v>892</v>
-      </c>
-      <c r="O519" s="2"/>
+        <v>884</v>
+      </c>
+      <c r="O519" t="s" s="2">
+        <v>885</v>
+      </c>
       <c r="P519" t="s" s="2">
         <v>78</v>
       </c>
@@ -65215,13 +65232,11 @@
         <v>78</v>
       </c>
       <c r="X519" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y519" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>175</v>
+      </c>
+      <c r="Y519" s="2"/>
       <c r="Z519" t="s" s="2">
-        <v>78</v>
+        <v>887</v>
       </c>
       <c r="AA519" t="s" s="2">
         <v>78</v>
@@ -65239,16 +65254,16 @@
         <v>78</v>
       </c>
       <c r="AF519" t="s" s="2">
-        <v>889</v>
+        <v>881</v>
       </c>
       <c r="AG519" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH519" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI519" t="s" s="2">
-        <v>856</v>
+        <v>878</v>
       </c>
       <c r="AJ519" t="s" s="2">
         <v>103</v>
@@ -65257,10 +65272,10 @@
         <v>78</v>
       </c>
       <c r="AL519" t="s" s="2">
-        <v>818</v>
+        <v>888</v>
       </c>
       <c r="AM519" t="s" s="2">
-        <v>893</v>
+        <v>109</v>
       </c>
       <c r="AN519" t="s" s="2">
         <v>78</v>
@@ -65269,16 +65284,14 @@
         <v>78</v>
       </c>
     </row>
-    <row r="520">
+    <row r="520" hidden="true">
       <c r="A520" t="s" s="2">
-        <v>1291</v>
+        <v>1294</v>
       </c>
       <c r="B520" t="s" s="2">
-        <v>812</v>
-      </c>
-      <c r="C520" t="s" s="2">
-        <v>1292</v>
-      </c>
+        <v>889</v>
+      </c>
+      <c r="C520" s="2"/>
       <c r="D520" t="s" s="2">
         <v>78</v>
       </c>
@@ -65287,10 +65300,10 @@
         <v>79</v>
       </c>
       <c r="G520" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H520" t="s" s="2">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="I520" t="s" s="2">
         <v>78</v>
@@ -65299,15 +65312,17 @@
         <v>78</v>
       </c>
       <c r="K520" t="s" s="2">
-        <v>568</v>
+        <v>81</v>
       </c>
       <c r="L520" t="s" s="2">
-        <v>1293</v>
+        <v>890</v>
       </c>
       <c r="M520" t="s" s="2">
-        <v>1294</v>
-      </c>
-      <c r="N520" s="2"/>
+        <v>891</v>
+      </c>
+      <c r="N520" t="s" s="2">
+        <v>892</v>
+      </c>
       <c r="O520" s="2"/>
       <c r="P520" t="s" s="2">
         <v>78</v>
@@ -65356,7 +65371,7 @@
         <v>78</v>
       </c>
       <c r="AF520" t="s" s="2">
-        <v>812</v>
+        <v>889</v>
       </c>
       <c r="AG520" t="s" s="2">
         <v>79</v>
@@ -65365,10 +65380,10 @@
         <v>80</v>
       </c>
       <c r="AI520" t="s" s="2">
-        <v>78</v>
+        <v>856</v>
       </c>
       <c r="AJ520" t="s" s="2">
-        <v>817</v>
+        <v>103</v>
       </c>
       <c r="AK520" t="s" s="2">
         <v>78</v>
@@ -65377,7 +65392,7 @@
         <v>818</v>
       </c>
       <c r="AM520" t="s" s="2">
-        <v>819</v>
+        <v>893</v>
       </c>
       <c r="AN520" t="s" s="2">
         <v>78</v>
@@ -65386,14 +65401,16 @@
         <v>78</v>
       </c>
     </row>
-    <row r="521" hidden="true">
+    <row r="521">
       <c r="A521" t="s" s="2">
         <v>1295</v>
       </c>
       <c r="B521" t="s" s="2">
-        <v>820</v>
-      </c>
-      <c r="C521" s="2"/>
+        <v>812</v>
+      </c>
+      <c r="C521" t="s" s="2">
+        <v>1296</v>
+      </c>
       <c r="D521" t="s" s="2">
         <v>78</v>
       </c>
@@ -65405,7 +65422,7 @@
         <v>91</v>
       </c>
       <c r="H521" t="s" s="2">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="I521" t="s" s="2">
         <v>78</v>
@@ -65414,13 +65431,13 @@
         <v>78</v>
       </c>
       <c r="K521" t="s" s="2">
-        <v>105</v>
+        <v>568</v>
       </c>
       <c r="L521" t="s" s="2">
-        <v>106</v>
+        <v>1297</v>
       </c>
       <c r="M521" t="s" s="2">
-        <v>107</v>
+        <v>1298</v>
       </c>
       <c r="N521" s="2"/>
       <c r="O521" s="2"/>
@@ -65471,28 +65488,28 @@
         <v>78</v>
       </c>
       <c r="AF521" t="s" s="2">
-        <v>108</v>
+        <v>812</v>
       </c>
       <c r="AG521" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH521" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI521" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ521" t="s" s="2">
-        <v>78</v>
+        <v>817</v>
       </c>
       <c r="AK521" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL521" t="s" s="2">
-        <v>109</v>
+        <v>818</v>
       </c>
       <c r="AM521" t="s" s="2">
-        <v>78</v>
+        <v>819</v>
       </c>
       <c r="AN521" t="s" s="2">
         <v>78</v>
@@ -65503,10 +65520,10 @@
     </row>
     <row r="522" hidden="true">
       <c r="A522" t="s" s="2">
-        <v>1296</v>
+        <v>1299</v>
       </c>
       <c r="B522" t="s" s="2">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="C522" s="2"/>
       <c r="D522" t="s" s="2">
@@ -65517,7 +65534,7 @@
         <v>79</v>
       </c>
       <c r="G522" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H522" t="s" s="2">
         <v>78</v>
@@ -65529,13 +65546,13 @@
         <v>78</v>
       </c>
       <c r="K522" t="s" s="2">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="L522" t="s" s="2">
-        <v>197</v>
+        <v>106</v>
       </c>
       <c r="M522" t="s" s="2">
-        <v>198</v>
+        <v>107</v>
       </c>
       <c r="N522" s="2"/>
       <c r="O522" s="2"/>
@@ -65574,35 +65591,37 @@
         <v>78</v>
       </c>
       <c r="AB522" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="AC522" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="AC522" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="AD522" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE522" t="s" s="2">
-        <v>118</v>
+        <v>78</v>
       </c>
       <c r="AF522" t="s" s="2">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="AG522" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH522" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI522" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ522" t="s" s="2">
-        <v>120</v>
+        <v>78</v>
       </c>
       <c r="AK522" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL522" t="s" s="2">
-        <v>78</v>
+        <v>109</v>
       </c>
       <c r="AM522" t="s" s="2">
         <v>78</v>
@@ -65616,14 +65635,12 @@
     </row>
     <row r="523" hidden="true">
       <c r="A523" t="s" s="2">
-        <v>1297</v>
+        <v>1300</v>
       </c>
       <c r="B523" t="s" s="2">
         <v>821</v>
       </c>
-      <c r="C523" t="s" s="2">
-        <v>405</v>
-      </c>
+      <c r="C523" s="2"/>
       <c r="D523" t="s" s="2">
         <v>78</v>
       </c>
@@ -65632,7 +65649,7 @@
         <v>79</v>
       </c>
       <c r="G523" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H523" t="s" s="2">
         <v>78</v>
@@ -65644,13 +65661,13 @@
         <v>78</v>
       </c>
       <c r="K523" t="s" s="2">
-        <v>407</v>
+        <v>112</v>
       </c>
       <c r="L523" t="s" s="2">
-        <v>823</v>
+        <v>197</v>
       </c>
       <c r="M523" t="s" s="2">
-        <v>408</v>
+        <v>198</v>
       </c>
       <c r="N523" s="2"/>
       <c r="O523" s="2"/>
@@ -65689,16 +65706,14 @@
         <v>78</v>
       </c>
       <c r="AB523" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC523" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>116</v>
+      </c>
+      <c r="AC523" s="2"/>
       <c r="AD523" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE523" t="s" s="2">
-        <v>78</v>
+        <v>118</v>
       </c>
       <c r="AF523" t="s" s="2">
         <v>119</v>
@@ -65710,7 +65725,7 @@
         <v>80</v>
       </c>
       <c r="AI523" t="s" s="2">
-        <v>207</v>
+        <v>78</v>
       </c>
       <c r="AJ523" t="s" s="2">
         <v>120</v>
@@ -65733,13 +65748,13 @@
     </row>
     <row r="524" hidden="true">
       <c r="A524" t="s" s="2">
-        <v>1298</v>
+        <v>1301</v>
       </c>
       <c r="B524" t="s" s="2">
         <v>821</v>
       </c>
       <c r="C524" t="s" s="2">
-        <v>825</v>
+        <v>405</v>
       </c>
       <c r="D524" t="s" s="2">
         <v>78</v>
@@ -65749,7 +65764,7 @@
         <v>79</v>
       </c>
       <c r="G524" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H524" t="s" s="2">
         <v>78</v>
@@ -65761,17 +65776,15 @@
         <v>78</v>
       </c>
       <c r="K524" t="s" s="2">
-        <v>826</v>
+        <v>407</v>
       </c>
       <c r="L524" t="s" s="2">
-        <v>827</v>
+        <v>823</v>
       </c>
       <c r="M524" t="s" s="2">
-        <v>828</v>
-      </c>
-      <c r="N524" t="s" s="2">
-        <v>829</v>
-      </c>
+        <v>408</v>
+      </c>
+      <c r="N524" s="2"/>
       <c r="O524" s="2"/>
       <c r="P524" t="s" s="2">
         <v>78</v>
@@ -65829,7 +65842,7 @@
         <v>80</v>
       </c>
       <c r="AI524" t="s" s="2">
-        <v>78</v>
+        <v>207</v>
       </c>
       <c r="AJ524" t="s" s="2">
         <v>120</v>
@@ -65852,14 +65865,16 @@
     </row>
     <row r="525" hidden="true">
       <c r="A525" t="s" s="2">
-        <v>1299</v>
+        <v>1302</v>
       </c>
       <c r="B525" t="s" s="2">
-        <v>830</v>
-      </c>
-      <c r="C525" s="2"/>
+        <v>821</v>
+      </c>
+      <c r="C525" t="s" s="2">
+        <v>825</v>
+      </c>
       <c r="D525" t="s" s="2">
-        <v>581</v>
+        <v>78</v>
       </c>
       <c r="E525" s="2"/>
       <c r="F525" t="s" s="2">
@@ -65872,26 +65887,24 @@
         <v>78</v>
       </c>
       <c r="I525" t="s" s="2">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="J525" t="s" s="2">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="K525" t="s" s="2">
-        <v>112</v>
+        <v>826</v>
       </c>
       <c r="L525" t="s" s="2">
-        <v>582</v>
+        <v>827</v>
       </c>
       <c r="M525" t="s" s="2">
-        <v>583</v>
+        <v>828</v>
       </c>
       <c r="N525" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="O525" t="s" s="2">
-        <v>412</v>
-      </c>
+        <v>829</v>
+      </c>
+      <c r="O525" s="2"/>
       <c r="P525" t="s" s="2">
         <v>78</v>
       </c>
@@ -65939,7 +65952,7 @@
         <v>78</v>
       </c>
       <c r="AF525" t="s" s="2">
-        <v>584</v>
+        <v>119</v>
       </c>
       <c r="AG525" t="s" s="2">
         <v>79</v>
@@ -65957,7 +65970,7 @@
         <v>78</v>
       </c>
       <c r="AL525" t="s" s="2">
-        <v>195</v>
+        <v>78</v>
       </c>
       <c r="AM525" t="s" s="2">
         <v>78</v>
@@ -65969,47 +65982,47 @@
         <v>78</v>
       </c>
     </row>
-    <row r="526">
+    <row r="526" hidden="true">
       <c r="A526" t="s" s="2">
-        <v>1300</v>
+        <v>1303</v>
       </c>
       <c r="B526" t="s" s="2">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="C526" s="2"/>
       <c r="D526" t="s" s="2">
-        <v>832</v>
+        <v>581</v>
       </c>
       <c r="E526" s="2"/>
       <c r="F526" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="G526" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H526" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I526" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="I526" t="s" s="2">
-        <v>78</v>
-      </c>
       <c r="J526" t="s" s="2">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="K526" t="s" s="2">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="L526" t="s" s="2">
-        <v>1301</v>
+        <v>582</v>
       </c>
       <c r="M526" t="s" s="2">
-        <v>834</v>
+        <v>583</v>
       </c>
       <c r="N526" t="s" s="2">
-        <v>835</v>
+        <v>115</v>
       </c>
       <c r="O526" t="s" s="2">
-        <v>836</v>
+        <v>412</v>
       </c>
       <c r="P526" t="s" s="2">
         <v>78</v>
@@ -66058,28 +66071,28 @@
         <v>78</v>
       </c>
       <c r="AF526" t="s" s="2">
-        <v>831</v>
+        <v>584</v>
       </c>
       <c r="AG526" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH526" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI526" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ526" t="s" s="2">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="AK526" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL526" t="s" s="2">
-        <v>556</v>
+        <v>195</v>
       </c>
       <c r="AM526" t="s" s="2">
-        <v>557</v>
+        <v>78</v>
       </c>
       <c r="AN526" t="s" s="2">
         <v>78</v>
@@ -66090,14 +66103,14 @@
     </row>
     <row r="527">
       <c r="A527" t="s" s="2">
-        <v>1302</v>
+        <v>1304</v>
       </c>
       <c r="B527" t="s" s="2">
-        <v>837</v>
+        <v>831</v>
       </c>
       <c r="C527" s="2"/>
       <c r="D527" t="s" s="2">
-        <v>78</v>
+        <v>832</v>
       </c>
       <c r="E527" s="2"/>
       <c r="F527" t="s" s="2">
@@ -66116,19 +66129,19 @@
         <v>78</v>
       </c>
       <c r="K527" t="s" s="2">
-        <v>235</v>
+        <v>105</v>
       </c>
       <c r="L527" t="s" s="2">
-        <v>838</v>
+        <v>1305</v>
       </c>
       <c r="M527" t="s" s="2">
-        <v>839</v>
+        <v>834</v>
       </c>
       <c r="N527" t="s" s="2">
-        <v>840</v>
+        <v>835</v>
       </c>
       <c r="O527" t="s" s="2">
-        <v>841</v>
+        <v>836</v>
       </c>
       <c r="P527" t="s" s="2">
         <v>78</v>
@@ -66138,7 +66151,7 @@
         <v>78</v>
       </c>
       <c r="S527" t="s" s="2">
-        <v>1303</v>
+        <v>78</v>
       </c>
       <c r="T527" t="s" s="2">
         <v>78</v>
@@ -66153,11 +66166,13 @@
         <v>78</v>
       </c>
       <c r="X527" t="s" s="2">
-        <v>325</v>
-      </c>
-      <c r="Y527" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y527" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z527" t="s" s="2">
-        <v>842</v>
+        <v>78</v>
       </c>
       <c r="AA527" t="s" s="2">
         <v>78</v>
@@ -66175,7 +66190,7 @@
         <v>78</v>
       </c>
       <c r="AF527" t="s" s="2">
-        <v>837</v>
+        <v>831</v>
       </c>
       <c r="AG527" t="s" s="2">
         <v>79</v>
@@ -66193,10 +66208,10 @@
         <v>78</v>
       </c>
       <c r="AL527" t="s" s="2">
-        <v>457</v>
+        <v>556</v>
       </c>
       <c r="AM527" t="s" s="2">
-        <v>458</v>
+        <v>557</v>
       </c>
       <c r="AN527" t="s" s="2">
         <v>78</v>
@@ -66205,12 +66220,12 @@
         <v>78</v>
       </c>
     </row>
-    <row r="528" hidden="true">
+    <row r="528">
       <c r="A528" t="s" s="2">
-        <v>1304</v>
+        <v>1306</v>
       </c>
       <c r="B528" t="s" s="2">
-        <v>843</v>
+        <v>837</v>
       </c>
       <c r="C528" s="2"/>
       <c r="D528" t="s" s="2">
@@ -66218,13 +66233,13 @@
       </c>
       <c r="E528" s="2"/>
       <c r="F528" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="G528" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H528" t="s" s="2">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="I528" t="s" s="2">
         <v>78</v>
@@ -66233,17 +66248,19 @@
         <v>78</v>
       </c>
       <c r="K528" t="s" s="2">
-        <v>844</v>
+        <v>235</v>
       </c>
       <c r="L528" t="s" s="2">
-        <v>845</v>
+        <v>838</v>
       </c>
       <c r="M528" t="s" s="2">
-        <v>846</v>
-      </c>
-      <c r="N528" s="2"/>
+        <v>839</v>
+      </c>
+      <c r="N528" t="s" s="2">
+        <v>840</v>
+      </c>
       <c r="O528" t="s" s="2">
-        <v>536</v>
+        <v>841</v>
       </c>
       <c r="P528" t="s" s="2">
         <v>78</v>
@@ -66253,7 +66270,7 @@
         <v>78</v>
       </c>
       <c r="S528" t="s" s="2">
-        <v>78</v>
+        <v>1307</v>
       </c>
       <c r="T528" t="s" s="2">
         <v>78</v>
@@ -66268,13 +66285,11 @@
         <v>78</v>
       </c>
       <c r="X528" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y528" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>325</v>
+      </c>
+      <c r="Y528" s="2"/>
       <c r="Z528" t="s" s="2">
-        <v>78</v>
+        <v>842</v>
       </c>
       <c r="AA528" t="s" s="2">
         <v>78</v>
@@ -66292,13 +66307,13 @@
         <v>78</v>
       </c>
       <c r="AF528" t="s" s="2">
-        <v>843</v>
+        <v>837</v>
       </c>
       <c r="AG528" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH528" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI528" t="s" s="2">
         <v>78</v>
@@ -66310,24 +66325,24 @@
         <v>78</v>
       </c>
       <c r="AL528" t="s" s="2">
-        <v>538</v>
+        <v>457</v>
       </c>
       <c r="AM528" t="s" s="2">
-        <v>539</v>
+        <v>458</v>
       </c>
       <c r="AN528" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO528" t="s" s="2">
-        <v>541</v>
+        <v>78</v>
       </c>
     </row>
     <row r="529" hidden="true">
       <c r="A529" t="s" s="2">
-        <v>1305</v>
+        <v>1308</v>
       </c>
       <c r="B529" t="s" s="2">
-        <v>847</v>
+        <v>843</v>
       </c>
       <c r="C529" s="2"/>
       <c r="D529" t="s" s="2">
@@ -66338,7 +66353,7 @@
         <v>79</v>
       </c>
       <c r="G529" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H529" t="s" s="2">
         <v>78</v>
@@ -66350,18 +66365,18 @@
         <v>78</v>
       </c>
       <c r="K529" t="s" s="2">
-        <v>797</v>
+        <v>844</v>
       </c>
       <c r="L529" t="s" s="2">
-        <v>848</v>
+        <v>845</v>
       </c>
       <c r="M529" t="s" s="2">
-        <v>849</v>
-      </c>
-      <c r="N529" t="s" s="2">
-        <v>850</v>
-      </c>
-      <c r="O529" s="2"/>
+        <v>846</v>
+      </c>
+      <c r="N529" s="2"/>
+      <c r="O529" t="s" s="2">
+        <v>536</v>
+      </c>
       <c r="P529" t="s" s="2">
         <v>78</v>
       </c>
@@ -66409,13 +66424,13 @@
         <v>78</v>
       </c>
       <c r="AF529" t="s" s="2">
-        <v>847</v>
+        <v>843</v>
       </c>
       <c r="AG529" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH529" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI529" t="s" s="2">
         <v>78</v>
@@ -66427,24 +66442,24 @@
         <v>78</v>
       </c>
       <c r="AL529" t="s" s="2">
-        <v>78</v>
+        <v>538</v>
       </c>
       <c r="AM529" t="s" s="2">
-        <v>851</v>
+        <v>539</v>
       </c>
       <c r="AN529" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO529" t="s" s="2">
-        <v>78</v>
+        <v>541</v>
       </c>
     </row>
-    <row r="530">
+    <row r="530" hidden="true">
       <c r="A530" t="s" s="2">
-        <v>1306</v>
+        <v>1309</v>
       </c>
       <c r="B530" t="s" s="2">
-        <v>852</v>
+        <v>847</v>
       </c>
       <c r="C530" s="2"/>
       <c r="D530" t="s" s="2">
@@ -66452,13 +66467,13 @@
       </c>
       <c r="E530" s="2"/>
       <c r="F530" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="G530" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H530" t="s" s="2">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="I530" t="s" s="2">
         <v>78</v>
@@ -66467,16 +66482,16 @@
         <v>78</v>
       </c>
       <c r="K530" t="s" s="2">
-        <v>182</v>
+        <v>797</v>
       </c>
       <c r="L530" t="s" s="2">
-        <v>1307</v>
+        <v>848</v>
       </c>
       <c r="M530" t="s" s="2">
-        <v>854</v>
+        <v>849</v>
       </c>
       <c r="N530" t="s" s="2">
-        <v>855</v>
+        <v>850</v>
       </c>
       <c r="O530" s="2"/>
       <c r="P530" t="s" s="2">
@@ -66526,7 +66541,7 @@
         <v>78</v>
       </c>
       <c r="AF530" t="s" s="2">
-        <v>852</v>
+        <v>847</v>
       </c>
       <c r="AG530" t="s" s="2">
         <v>79</v>
@@ -66535,7 +66550,7 @@
         <v>91</v>
       </c>
       <c r="AI530" t="s" s="2">
-        <v>856</v>
+        <v>78</v>
       </c>
       <c r="AJ530" t="s" s="2">
         <v>103</v>
@@ -66544,10 +66559,10 @@
         <v>78</v>
       </c>
       <c r="AL530" t="s" s="2">
-        <v>857</v>
+        <v>78</v>
       </c>
       <c r="AM530" t="s" s="2">
-        <v>857</v>
+        <v>851</v>
       </c>
       <c r="AN530" t="s" s="2">
         <v>78</v>
@@ -66556,12 +66571,12 @@
         <v>78</v>
       </c>
     </row>
-    <row r="531" hidden="true">
+    <row r="531">
       <c r="A531" t="s" s="2">
-        <v>1308</v>
+        <v>1310</v>
       </c>
       <c r="B531" t="s" s="2">
-        <v>858</v>
+        <v>852</v>
       </c>
       <c r="C531" s="2"/>
       <c r="D531" t="s" s="2">
@@ -66569,13 +66584,13 @@
       </c>
       <c r="E531" s="2"/>
       <c r="F531" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="G531" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H531" t="s" s="2">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="I531" t="s" s="2">
         <v>78</v>
@@ -66584,20 +66599,18 @@
         <v>78</v>
       </c>
       <c r="K531" t="s" s="2">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="L531" t="s" s="2">
-        <v>859</v>
+        <v>1311</v>
       </c>
       <c r="M531" t="s" s="2">
-        <v>860</v>
+        <v>854</v>
       </c>
       <c r="N531" t="s" s="2">
-        <v>861</v>
-      </c>
-      <c r="O531" t="s" s="2">
-        <v>862</v>
-      </c>
+        <v>855</v>
+      </c>
+      <c r="O531" s="2"/>
       <c r="P531" t="s" s="2">
         <v>78</v>
       </c>
@@ -66621,13 +66634,13 @@
         <v>78</v>
       </c>
       <c r="X531" t="s" s="2">
-        <v>325</v>
+        <v>78</v>
       </c>
       <c r="Y531" t="s" s="2">
-        <v>863</v>
+        <v>78</v>
       </c>
       <c r="Z531" t="s" s="2">
-        <v>864</v>
+        <v>78</v>
       </c>
       <c r="AA531" t="s" s="2">
         <v>78</v>
@@ -66645,7 +66658,7 @@
         <v>78</v>
       </c>
       <c r="AF531" t="s" s="2">
-        <v>858</v>
+        <v>852</v>
       </c>
       <c r="AG531" t="s" s="2">
         <v>79</v>
@@ -66654,7 +66667,7 @@
         <v>91</v>
       </c>
       <c r="AI531" t="s" s="2">
-        <v>78</v>
+        <v>856</v>
       </c>
       <c r="AJ531" t="s" s="2">
         <v>103</v>
@@ -66663,24 +66676,24 @@
         <v>78</v>
       </c>
       <c r="AL531" t="s" s="2">
-        <v>865</v>
+        <v>857</v>
       </c>
       <c r="AM531" t="s" s="2">
-        <v>109</v>
+        <v>857</v>
       </c>
       <c r="AN531" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO531" t="s" s="2">
-        <v>460</v>
+        <v>78</v>
       </c>
     </row>
     <row r="532" hidden="true">
       <c r="A532" t="s" s="2">
-        <v>1309</v>
+        <v>1312</v>
       </c>
       <c r="B532" t="s" s="2">
-        <v>866</v>
+        <v>858</v>
       </c>
       <c r="C532" s="2"/>
       <c r="D532" t="s" s="2">
@@ -66703,19 +66716,19 @@
         <v>78</v>
       </c>
       <c r="K532" t="s" s="2">
-        <v>235</v>
+        <v>171</v>
       </c>
       <c r="L532" t="s" s="2">
-        <v>867</v>
+        <v>859</v>
       </c>
       <c r="M532" t="s" s="2">
-        <v>868</v>
+        <v>860</v>
       </c>
       <c r="N532" t="s" s="2">
-        <v>869</v>
+        <v>861</v>
       </c>
       <c r="O532" t="s" s="2">
-        <v>870</v>
+        <v>862</v>
       </c>
       <c r="P532" t="s" s="2">
         <v>78</v>
@@ -66740,13 +66753,13 @@
         <v>78</v>
       </c>
       <c r="X532" t="s" s="2">
-        <v>175</v>
+        <v>325</v>
       </c>
       <c r="Y532" t="s" s="2">
-        <v>871</v>
+        <v>863</v>
       </c>
       <c r="Z532" t="s" s="2">
-        <v>872</v>
+        <v>864</v>
       </c>
       <c r="AA532" t="s" s="2">
         <v>78</v>
@@ -66764,7 +66777,7 @@
         <v>78</v>
       </c>
       <c r="AF532" t="s" s="2">
-        <v>866</v>
+        <v>858</v>
       </c>
       <c r="AG532" t="s" s="2">
         <v>79</v>
@@ -66782,7 +66795,7 @@
         <v>78</v>
       </c>
       <c r="AL532" t="s" s="2">
-        <v>873</v>
+        <v>865</v>
       </c>
       <c r="AM532" t="s" s="2">
         <v>109</v>
@@ -66791,15 +66804,15 @@
         <v>78</v>
       </c>
       <c r="AO532" t="s" s="2">
-        <v>78</v>
+        <v>460</v>
       </c>
     </row>
     <row r="533" hidden="true">
       <c r="A533" t="s" s="2">
-        <v>1310</v>
+        <v>1313</v>
       </c>
       <c r="B533" t="s" s="2">
-        <v>874</v>
+        <v>866</v>
       </c>
       <c r="C533" s="2"/>
       <c r="D533" t="s" s="2">
@@ -66810,7 +66823,7 @@
         <v>79</v>
       </c>
       <c r="G533" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H533" t="s" s="2">
         <v>78</v>
@@ -66822,18 +66835,20 @@
         <v>78</v>
       </c>
       <c r="K533" t="s" s="2">
-        <v>797</v>
+        <v>235</v>
       </c>
       <c r="L533" t="s" s="2">
-        <v>875</v>
+        <v>867</v>
       </c>
       <c r="M533" t="s" s="2">
-        <v>876</v>
+        <v>868</v>
       </c>
       <c r="N533" t="s" s="2">
-        <v>877</v>
-      </c>
-      <c r="O533" s="2"/>
+        <v>869</v>
+      </c>
+      <c r="O533" t="s" s="2">
+        <v>870</v>
+      </c>
       <c r="P533" t="s" s="2">
         <v>78</v>
       </c>
@@ -66857,38 +66872,40 @@
         <v>78</v>
       </c>
       <c r="X533" t="s" s="2">
-        <v>78</v>
+        <v>175</v>
       </c>
       <c r="Y533" t="s" s="2">
-        <v>78</v>
+        <v>871</v>
       </c>
       <c r="Z533" t="s" s="2">
-        <v>78</v>
+        <v>872</v>
       </c>
       <c r="AA533" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AB533" t="s" s="2">
-        <v>915</v>
-      </c>
-      <c r="AC533" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="AC533" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="AD533" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE533" t="s" s="2">
-        <v>118</v>
+        <v>78</v>
       </c>
       <c r="AF533" t="s" s="2">
-        <v>874</v>
+        <v>866</v>
       </c>
       <c r="AG533" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH533" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI533" t="s" s="2">
-        <v>878</v>
+        <v>78</v>
       </c>
       <c r="AJ533" t="s" s="2">
         <v>103</v>
@@ -66897,10 +66914,10 @@
         <v>78</v>
       </c>
       <c r="AL533" t="s" s="2">
-        <v>879</v>
+        <v>873</v>
       </c>
       <c r="AM533" t="s" s="2">
-        <v>880</v>
+        <v>109</v>
       </c>
       <c r="AN533" t="s" s="2">
         <v>78</v>
@@ -66911,14 +66928,12 @@
     </row>
     <row r="534" hidden="true">
       <c r="A534" t="s" s="2">
-        <v>1311</v>
+        <v>1314</v>
       </c>
       <c r="B534" t="s" s="2">
         <v>874</v>
       </c>
-      <c r="C534" t="s" s="2">
-        <v>1312</v>
-      </c>
+      <c r="C534" s="2"/>
       <c r="D534" t="s" s="2">
         <v>78</v>
       </c>
@@ -66939,10 +66954,10 @@
         <v>78</v>
       </c>
       <c r="K534" t="s" s="2">
-        <v>1313</v>
+        <v>797</v>
       </c>
       <c r="L534" t="s" s="2">
-        <v>1314</v>
+        <v>875</v>
       </c>
       <c r="M534" t="s" s="2">
         <v>876</v>
@@ -66986,16 +67001,14 @@
         <v>78</v>
       </c>
       <c r="AB534" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC534" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>915</v>
+      </c>
+      <c r="AC534" s="2"/>
       <c r="AD534" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE534" t="s" s="2">
-        <v>78</v>
+        <v>118</v>
       </c>
       <c r="AF534" t="s" s="2">
         <v>874</v>
@@ -67028,14 +67041,16 @@
         <v>78</v>
       </c>
     </row>
-    <row r="535">
+    <row r="535" hidden="true">
       <c r="A535" t="s" s="2">
         <v>1315</v>
       </c>
       <c r="B535" t="s" s="2">
-        <v>881</v>
-      </c>
-      <c r="C535" s="2"/>
+        <v>874</v>
+      </c>
+      <c r="C535" t="s" s="2">
+        <v>1316</v>
+      </c>
       <c r="D535" t="s" s="2">
         <v>78</v>
       </c>
@@ -67044,10 +67059,10 @@
         <v>79</v>
       </c>
       <c r="G535" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H535" t="s" s="2">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="I535" t="s" s="2">
         <v>78</v>
@@ -67056,20 +67071,18 @@
         <v>78</v>
       </c>
       <c r="K535" t="s" s="2">
-        <v>235</v>
+        <v>1317</v>
       </c>
       <c r="L535" t="s" s="2">
-        <v>921</v>
+        <v>1318</v>
       </c>
       <c r="M535" t="s" s="2">
-        <v>883</v>
+        <v>876</v>
       </c>
       <c r="N535" t="s" s="2">
-        <v>884</v>
-      </c>
-      <c r="O535" t="s" s="2">
-        <v>885</v>
-      </c>
+        <v>877</v>
+      </c>
+      <c r="O535" s="2"/>
       <c r="P535" t="s" s="2">
         <v>78</v>
       </c>
@@ -67093,11 +67106,13 @@
         <v>78</v>
       </c>
       <c r="X535" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="Y535" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y535" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z535" t="s" s="2">
-        <v>887</v>
+        <v>78</v>
       </c>
       <c r="AA535" t="s" s="2">
         <v>78</v>
@@ -67115,13 +67130,13 @@
         <v>78</v>
       </c>
       <c r="AF535" t="s" s="2">
-        <v>881</v>
+        <v>874</v>
       </c>
       <c r="AG535" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH535" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI535" t="s" s="2">
         <v>878</v>
@@ -67133,10 +67148,10 @@
         <v>78</v>
       </c>
       <c r="AL535" t="s" s="2">
-        <v>888</v>
+        <v>879</v>
       </c>
       <c r="AM535" t="s" s="2">
-        <v>109</v>
+        <v>880</v>
       </c>
       <c r="AN535" t="s" s="2">
         <v>78</v>
@@ -67145,12 +67160,12 @@
         <v>78</v>
       </c>
     </row>
-    <row r="536" hidden="true">
+    <row r="536">
       <c r="A536" t="s" s="2">
-        <v>1316</v>
+        <v>1319</v>
       </c>
       <c r="B536" t="s" s="2">
-        <v>889</v>
+        <v>881</v>
       </c>
       <c r="C536" s="2"/>
       <c r="D536" t="s" s="2">
@@ -67161,10 +67176,10 @@
         <v>79</v>
       </c>
       <c r="G536" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H536" t="s" s="2">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="I536" t="s" s="2">
         <v>78</v>
@@ -67173,18 +67188,20 @@
         <v>78</v>
       </c>
       <c r="K536" t="s" s="2">
-        <v>81</v>
+        <v>235</v>
       </c>
       <c r="L536" t="s" s="2">
-        <v>890</v>
+        <v>921</v>
       </c>
       <c r="M536" t="s" s="2">
-        <v>891</v>
+        <v>883</v>
       </c>
       <c r="N536" t="s" s="2">
-        <v>892</v>
-      </c>
-      <c r="O536" s="2"/>
+        <v>884</v>
+      </c>
+      <c r="O536" t="s" s="2">
+        <v>885</v>
+      </c>
       <c r="P536" t="s" s="2">
         <v>78</v>
       </c>
@@ -67208,13 +67225,11 @@
         <v>78</v>
       </c>
       <c r="X536" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y536" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>175</v>
+      </c>
+      <c r="Y536" s="2"/>
       <c r="Z536" t="s" s="2">
-        <v>78</v>
+        <v>887</v>
       </c>
       <c r="AA536" t="s" s="2">
         <v>78</v>
@@ -67232,16 +67247,16 @@
         <v>78</v>
       </c>
       <c r="AF536" t="s" s="2">
-        <v>889</v>
+        <v>881</v>
       </c>
       <c r="AG536" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH536" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI536" t="s" s="2">
-        <v>856</v>
+        <v>878</v>
       </c>
       <c r="AJ536" t="s" s="2">
         <v>103</v>
@@ -67250,10 +67265,10 @@
         <v>78</v>
       </c>
       <c r="AL536" t="s" s="2">
-        <v>818</v>
+        <v>888</v>
       </c>
       <c r="AM536" t="s" s="2">
-        <v>893</v>
+        <v>109</v>
       </c>
       <c r="AN536" t="s" s="2">
         <v>78</v>
@@ -67262,16 +67277,14 @@
         <v>78</v>
       </c>
     </row>
-    <row r="537">
+    <row r="537" hidden="true">
       <c r="A537" t="s" s="2">
-        <v>1317</v>
+        <v>1320</v>
       </c>
       <c r="B537" t="s" s="2">
-        <v>812</v>
-      </c>
-      <c r="C537" t="s" s="2">
-        <v>1318</v>
-      </c>
+        <v>889</v>
+      </c>
+      <c r="C537" s="2"/>
       <c r="D537" t="s" s="2">
         <v>78</v>
       </c>
@@ -67280,10 +67293,10 @@
         <v>79</v>
       </c>
       <c r="G537" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H537" t="s" s="2">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="I537" t="s" s="2">
         <v>78</v>
@@ -67292,15 +67305,17 @@
         <v>78</v>
       </c>
       <c r="K537" t="s" s="2">
-        <v>568</v>
+        <v>81</v>
       </c>
       <c r="L537" t="s" s="2">
-        <v>1319</v>
+        <v>890</v>
       </c>
       <c r="M537" t="s" s="2">
-        <v>1320</v>
-      </c>
-      <c r="N537" s="2"/>
+        <v>891</v>
+      </c>
+      <c r="N537" t="s" s="2">
+        <v>892</v>
+      </c>
       <c r="O537" s="2"/>
       <c r="P537" t="s" s="2">
         <v>78</v>
@@ -67349,7 +67364,7 @@
         <v>78</v>
       </c>
       <c r="AF537" t="s" s="2">
-        <v>812</v>
+        <v>889</v>
       </c>
       <c r="AG537" t="s" s="2">
         <v>79</v>
@@ -67358,10 +67373,10 @@
         <v>80</v>
       </c>
       <c r="AI537" t="s" s="2">
-        <v>78</v>
+        <v>856</v>
       </c>
       <c r="AJ537" t="s" s="2">
-        <v>817</v>
+        <v>103</v>
       </c>
       <c r="AK537" t="s" s="2">
         <v>78</v>
@@ -67370,7 +67385,7 @@
         <v>818</v>
       </c>
       <c r="AM537" t="s" s="2">
-        <v>819</v>
+        <v>893</v>
       </c>
       <c r="AN537" t="s" s="2">
         <v>78</v>
@@ -67379,14 +67394,16 @@
         <v>78</v>
       </c>
     </row>
-    <row r="538" hidden="true">
+    <row r="538">
       <c r="A538" t="s" s="2">
         <v>1321</v>
       </c>
       <c r="B538" t="s" s="2">
-        <v>820</v>
-      </c>
-      <c r="C538" s="2"/>
+        <v>812</v>
+      </c>
+      <c r="C538" t="s" s="2">
+        <v>1322</v>
+      </c>
       <c r="D538" t="s" s="2">
         <v>78</v>
       </c>
@@ -67398,7 +67415,7 @@
         <v>91</v>
       </c>
       <c r="H538" t="s" s="2">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="I538" t="s" s="2">
         <v>78</v>
@@ -67407,13 +67424,13 @@
         <v>78</v>
       </c>
       <c r="K538" t="s" s="2">
-        <v>105</v>
+        <v>568</v>
       </c>
       <c r="L538" t="s" s="2">
-        <v>106</v>
+        <v>1323</v>
       </c>
       <c r="M538" t="s" s="2">
-        <v>107</v>
+        <v>1324</v>
       </c>
       <c r="N538" s="2"/>
       <c r="O538" s="2"/>
@@ -67464,28 +67481,28 @@
         <v>78</v>
       </c>
       <c r="AF538" t="s" s="2">
-        <v>108</v>
+        <v>812</v>
       </c>
       <c r="AG538" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH538" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI538" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ538" t="s" s="2">
-        <v>78</v>
+        <v>817</v>
       </c>
       <c r="AK538" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL538" t="s" s="2">
-        <v>109</v>
+        <v>818</v>
       </c>
       <c r="AM538" t="s" s="2">
-        <v>78</v>
+        <v>819</v>
       </c>
       <c r="AN538" t="s" s="2">
         <v>78</v>
@@ -67496,10 +67513,10 @@
     </row>
     <row r="539" hidden="true">
       <c r="A539" t="s" s="2">
-        <v>1322</v>
+        <v>1325</v>
       </c>
       <c r="B539" t="s" s="2">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="C539" s="2"/>
       <c r="D539" t="s" s="2">
@@ -67510,7 +67527,7 @@
         <v>79</v>
       </c>
       <c r="G539" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H539" t="s" s="2">
         <v>78</v>
@@ -67522,13 +67539,13 @@
         <v>78</v>
       </c>
       <c r="K539" t="s" s="2">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="L539" t="s" s="2">
-        <v>197</v>
+        <v>106</v>
       </c>
       <c r="M539" t="s" s="2">
-        <v>198</v>
+        <v>107</v>
       </c>
       <c r="N539" s="2"/>
       <c r="O539" s="2"/>
@@ -67567,35 +67584,37 @@
         <v>78</v>
       </c>
       <c r="AB539" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="AC539" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="AC539" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="AD539" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE539" t="s" s="2">
-        <v>118</v>
+        <v>78</v>
       </c>
       <c r="AF539" t="s" s="2">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="AG539" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH539" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI539" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ539" t="s" s="2">
-        <v>120</v>
+        <v>78</v>
       </c>
       <c r="AK539" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL539" t="s" s="2">
-        <v>78</v>
+        <v>109</v>
       </c>
       <c r="AM539" t="s" s="2">
         <v>78</v>
@@ -67609,14 +67628,12 @@
     </row>
     <row r="540" hidden="true">
       <c r="A540" t="s" s="2">
-        <v>1323</v>
+        <v>1326</v>
       </c>
       <c r="B540" t="s" s="2">
         <v>821</v>
       </c>
-      <c r="C540" t="s" s="2">
-        <v>405</v>
-      </c>
+      <c r="C540" s="2"/>
       <c r="D540" t="s" s="2">
         <v>78</v>
       </c>
@@ -67625,7 +67642,7 @@
         <v>79</v>
       </c>
       <c r="G540" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H540" t="s" s="2">
         <v>78</v>
@@ -67637,13 +67654,13 @@
         <v>78</v>
       </c>
       <c r="K540" t="s" s="2">
-        <v>407</v>
+        <v>112</v>
       </c>
       <c r="L540" t="s" s="2">
-        <v>823</v>
+        <v>197</v>
       </c>
       <c r="M540" t="s" s="2">
-        <v>408</v>
+        <v>198</v>
       </c>
       <c r="N540" s="2"/>
       <c r="O540" s="2"/>
@@ -67682,16 +67699,14 @@
         <v>78</v>
       </c>
       <c r="AB540" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC540" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>116</v>
+      </c>
+      <c r="AC540" s="2"/>
       <c r="AD540" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE540" t="s" s="2">
-        <v>78</v>
+        <v>118</v>
       </c>
       <c r="AF540" t="s" s="2">
         <v>119</v>
@@ -67703,7 +67718,7 @@
         <v>80</v>
       </c>
       <c r="AI540" t="s" s="2">
-        <v>207</v>
+        <v>78</v>
       </c>
       <c r="AJ540" t="s" s="2">
         <v>120</v>
@@ -67726,13 +67741,13 @@
     </row>
     <row r="541" hidden="true">
       <c r="A541" t="s" s="2">
-        <v>1324</v>
+        <v>1327</v>
       </c>
       <c r="B541" t="s" s="2">
         <v>821</v>
       </c>
       <c r="C541" t="s" s="2">
-        <v>825</v>
+        <v>405</v>
       </c>
       <c r="D541" t="s" s="2">
         <v>78</v>
@@ -67742,7 +67757,7 @@
         <v>79</v>
       </c>
       <c r="G541" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H541" t="s" s="2">
         <v>78</v>
@@ -67754,17 +67769,15 @@
         <v>78</v>
       </c>
       <c r="K541" t="s" s="2">
-        <v>826</v>
+        <v>407</v>
       </c>
       <c r="L541" t="s" s="2">
-        <v>827</v>
+        <v>823</v>
       </c>
       <c r="M541" t="s" s="2">
-        <v>828</v>
-      </c>
-      <c r="N541" t="s" s="2">
-        <v>829</v>
-      </c>
+        <v>408</v>
+      </c>
+      <c r="N541" s="2"/>
       <c r="O541" s="2"/>
       <c r="P541" t="s" s="2">
         <v>78</v>
@@ -67822,7 +67835,7 @@
         <v>80</v>
       </c>
       <c r="AI541" t="s" s="2">
-        <v>78</v>
+        <v>207</v>
       </c>
       <c r="AJ541" t="s" s="2">
         <v>120</v>
@@ -67845,14 +67858,16 @@
     </row>
     <row r="542" hidden="true">
       <c r="A542" t="s" s="2">
-        <v>1325</v>
+        <v>1328</v>
       </c>
       <c r="B542" t="s" s="2">
-        <v>830</v>
-      </c>
-      <c r="C542" s="2"/>
+        <v>821</v>
+      </c>
+      <c r="C542" t="s" s="2">
+        <v>825</v>
+      </c>
       <c r="D542" t="s" s="2">
-        <v>581</v>
+        <v>78</v>
       </c>
       <c r="E542" s="2"/>
       <c r="F542" t="s" s="2">
@@ -67865,26 +67880,24 @@
         <v>78</v>
       </c>
       <c r="I542" t="s" s="2">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="J542" t="s" s="2">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="K542" t="s" s="2">
-        <v>112</v>
+        <v>826</v>
       </c>
       <c r="L542" t="s" s="2">
-        <v>582</v>
+        <v>827</v>
       </c>
       <c r="M542" t="s" s="2">
-        <v>583</v>
+        <v>828</v>
       </c>
       <c r="N542" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="O542" t="s" s="2">
-        <v>412</v>
-      </c>
+        <v>829</v>
+      </c>
+      <c r="O542" s="2"/>
       <c r="P542" t="s" s="2">
         <v>78</v>
       </c>
@@ -67932,7 +67945,7 @@
         <v>78</v>
       </c>
       <c r="AF542" t="s" s="2">
-        <v>584</v>
+        <v>119</v>
       </c>
       <c r="AG542" t="s" s="2">
         <v>79</v>
@@ -67950,7 +67963,7 @@
         <v>78</v>
       </c>
       <c r="AL542" t="s" s="2">
-        <v>195</v>
+        <v>78</v>
       </c>
       <c r="AM542" t="s" s="2">
         <v>78</v>
@@ -67962,47 +67975,47 @@
         <v>78</v>
       </c>
     </row>
-    <row r="543">
+    <row r="543" hidden="true">
       <c r="A543" t="s" s="2">
-        <v>1326</v>
+        <v>1329</v>
       </c>
       <c r="B543" t="s" s="2">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="C543" s="2"/>
       <c r="D543" t="s" s="2">
-        <v>832</v>
+        <v>581</v>
       </c>
       <c r="E543" s="2"/>
       <c r="F543" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="G543" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H543" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I543" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="I543" t="s" s="2">
-        <v>78</v>
-      </c>
       <c r="J543" t="s" s="2">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="K543" t="s" s="2">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="L543" t="s" s="2">
-        <v>1327</v>
+        <v>582</v>
       </c>
       <c r="M543" t="s" s="2">
-        <v>834</v>
+        <v>583</v>
       </c>
       <c r="N543" t="s" s="2">
-        <v>835</v>
+        <v>115</v>
       </c>
       <c r="O543" t="s" s="2">
-        <v>836</v>
+        <v>412</v>
       </c>
       <c r="P543" t="s" s="2">
         <v>78</v>
@@ -68051,28 +68064,28 @@
         <v>78</v>
       </c>
       <c r="AF543" t="s" s="2">
-        <v>831</v>
+        <v>584</v>
       </c>
       <c r="AG543" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH543" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI543" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ543" t="s" s="2">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="AK543" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL543" t="s" s="2">
-        <v>556</v>
+        <v>195</v>
       </c>
       <c r="AM543" t="s" s="2">
-        <v>557</v>
+        <v>78</v>
       </c>
       <c r="AN543" t="s" s="2">
         <v>78</v>
@@ -68083,14 +68096,14 @@
     </row>
     <row r="544">
       <c r="A544" t="s" s="2">
-        <v>1328</v>
+        <v>1330</v>
       </c>
       <c r="B544" t="s" s="2">
-        <v>837</v>
+        <v>831</v>
       </c>
       <c r="C544" s="2"/>
       <c r="D544" t="s" s="2">
-        <v>78</v>
+        <v>832</v>
       </c>
       <c r="E544" s="2"/>
       <c r="F544" t="s" s="2">
@@ -68109,19 +68122,19 @@
         <v>78</v>
       </c>
       <c r="K544" t="s" s="2">
-        <v>235</v>
+        <v>105</v>
       </c>
       <c r="L544" t="s" s="2">
-        <v>838</v>
+        <v>1331</v>
       </c>
       <c r="M544" t="s" s="2">
-        <v>839</v>
+        <v>834</v>
       </c>
       <c r="N544" t="s" s="2">
-        <v>840</v>
+        <v>835</v>
       </c>
       <c r="O544" t="s" s="2">
-        <v>841</v>
+        <v>836</v>
       </c>
       <c r="P544" t="s" s="2">
         <v>78</v>
@@ -68131,7 +68144,7 @@
         <v>78</v>
       </c>
       <c r="S544" t="s" s="2">
-        <v>1329</v>
+        <v>78</v>
       </c>
       <c r="T544" t="s" s="2">
         <v>78</v>
@@ -68146,11 +68159,13 @@
         <v>78</v>
       </c>
       <c r="X544" t="s" s="2">
-        <v>325</v>
-      </c>
-      <c r="Y544" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y544" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z544" t="s" s="2">
-        <v>842</v>
+        <v>78</v>
       </c>
       <c r="AA544" t="s" s="2">
         <v>78</v>
@@ -68168,7 +68183,7 @@
         <v>78</v>
       </c>
       <c r="AF544" t="s" s="2">
-        <v>837</v>
+        <v>831</v>
       </c>
       <c r="AG544" t="s" s="2">
         <v>79</v>
@@ -68186,10 +68201,10 @@
         <v>78</v>
       </c>
       <c r="AL544" t="s" s="2">
-        <v>457</v>
+        <v>556</v>
       </c>
       <c r="AM544" t="s" s="2">
-        <v>458</v>
+        <v>557</v>
       </c>
       <c r="AN544" t="s" s="2">
         <v>78</v>
@@ -68198,12 +68213,12 @@
         <v>78</v>
       </c>
     </row>
-    <row r="545" hidden="true">
+    <row r="545">
       <c r="A545" t="s" s="2">
-        <v>1330</v>
+        <v>1332</v>
       </c>
       <c r="B545" t="s" s="2">
-        <v>843</v>
+        <v>837</v>
       </c>
       <c r="C545" s="2"/>
       <c r="D545" t="s" s="2">
@@ -68211,13 +68226,13 @@
       </c>
       <c r="E545" s="2"/>
       <c r="F545" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="G545" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H545" t="s" s="2">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="I545" t="s" s="2">
         <v>78</v>
@@ -68226,17 +68241,19 @@
         <v>78</v>
       </c>
       <c r="K545" t="s" s="2">
-        <v>844</v>
+        <v>235</v>
       </c>
       <c r="L545" t="s" s="2">
-        <v>845</v>
+        <v>838</v>
       </c>
       <c r="M545" t="s" s="2">
-        <v>846</v>
-      </c>
-      <c r="N545" s="2"/>
+        <v>839</v>
+      </c>
+      <c r="N545" t="s" s="2">
+        <v>840</v>
+      </c>
       <c r="O545" t="s" s="2">
-        <v>536</v>
+        <v>841</v>
       </c>
       <c r="P545" t="s" s="2">
         <v>78</v>
@@ -68246,7 +68263,7 @@
         <v>78</v>
       </c>
       <c r="S545" t="s" s="2">
-        <v>78</v>
+        <v>1333</v>
       </c>
       <c r="T545" t="s" s="2">
         <v>78</v>
@@ -68261,13 +68278,11 @@
         <v>78</v>
       </c>
       <c r="X545" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y545" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>325</v>
+      </c>
+      <c r="Y545" s="2"/>
       <c r="Z545" t="s" s="2">
-        <v>78</v>
+        <v>842</v>
       </c>
       <c r="AA545" t="s" s="2">
         <v>78</v>
@@ -68285,13 +68300,13 @@
         <v>78</v>
       </c>
       <c r="AF545" t="s" s="2">
-        <v>843</v>
+        <v>837</v>
       </c>
       <c r="AG545" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH545" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI545" t="s" s="2">
         <v>78</v>
@@ -68303,24 +68318,24 @@
         <v>78</v>
       </c>
       <c r="AL545" t="s" s="2">
-        <v>538</v>
+        <v>457</v>
       </c>
       <c r="AM545" t="s" s="2">
-        <v>539</v>
+        <v>458</v>
       </c>
       <c r="AN545" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO545" t="s" s="2">
-        <v>541</v>
+        <v>78</v>
       </c>
     </row>
     <row r="546" hidden="true">
       <c r="A546" t="s" s="2">
-        <v>1331</v>
+        <v>1334</v>
       </c>
       <c r="B546" t="s" s="2">
-        <v>847</v>
+        <v>843</v>
       </c>
       <c r="C546" s="2"/>
       <c r="D546" t="s" s="2">
@@ -68331,7 +68346,7 @@
         <v>79</v>
       </c>
       <c r="G546" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H546" t="s" s="2">
         <v>78</v>
@@ -68343,18 +68358,18 @@
         <v>78</v>
       </c>
       <c r="K546" t="s" s="2">
-        <v>797</v>
+        <v>844</v>
       </c>
       <c r="L546" t="s" s="2">
-        <v>848</v>
+        <v>845</v>
       </c>
       <c r="M546" t="s" s="2">
-        <v>849</v>
-      </c>
-      <c r="N546" t="s" s="2">
-        <v>850</v>
-      </c>
-      <c r="O546" s="2"/>
+        <v>846</v>
+      </c>
+      <c r="N546" s="2"/>
+      <c r="O546" t="s" s="2">
+        <v>536</v>
+      </c>
       <c r="P546" t="s" s="2">
         <v>78</v>
       </c>
@@ -68402,13 +68417,13 @@
         <v>78</v>
       </c>
       <c r="AF546" t="s" s="2">
-        <v>847</v>
+        <v>843</v>
       </c>
       <c r="AG546" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH546" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI546" t="s" s="2">
         <v>78</v>
@@ -68420,24 +68435,24 @@
         <v>78</v>
       </c>
       <c r="AL546" t="s" s="2">
-        <v>78</v>
+        <v>538</v>
       </c>
       <c r="AM546" t="s" s="2">
-        <v>851</v>
+        <v>539</v>
       </c>
       <c r="AN546" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO546" t="s" s="2">
-        <v>78</v>
+        <v>541</v>
       </c>
     </row>
-    <row r="547">
+    <row r="547" hidden="true">
       <c r="A547" t="s" s="2">
-        <v>1332</v>
+        <v>1335</v>
       </c>
       <c r="B547" t="s" s="2">
-        <v>852</v>
+        <v>847</v>
       </c>
       <c r="C547" s="2"/>
       <c r="D547" t="s" s="2">
@@ -68445,13 +68460,13 @@
       </c>
       <c r="E547" s="2"/>
       <c r="F547" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="G547" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H547" t="s" s="2">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="I547" t="s" s="2">
         <v>78</v>
@@ -68460,16 +68475,16 @@
         <v>78</v>
       </c>
       <c r="K547" t="s" s="2">
-        <v>182</v>
+        <v>797</v>
       </c>
       <c r="L547" t="s" s="2">
-        <v>1333</v>
+        <v>848</v>
       </c>
       <c r="M547" t="s" s="2">
-        <v>854</v>
+        <v>849</v>
       </c>
       <c r="N547" t="s" s="2">
-        <v>855</v>
+        <v>850</v>
       </c>
       <c r="O547" s="2"/>
       <c r="P547" t="s" s="2">
@@ -68519,7 +68534,7 @@
         <v>78</v>
       </c>
       <c r="AF547" t="s" s="2">
-        <v>852</v>
+        <v>847</v>
       </c>
       <c r="AG547" t="s" s="2">
         <v>79</v>
@@ -68528,7 +68543,7 @@
         <v>91</v>
       </c>
       <c r="AI547" t="s" s="2">
-        <v>856</v>
+        <v>78</v>
       </c>
       <c r="AJ547" t="s" s="2">
         <v>103</v>
@@ -68537,10 +68552,10 @@
         <v>78</v>
       </c>
       <c r="AL547" t="s" s="2">
-        <v>857</v>
+        <v>78</v>
       </c>
       <c r="AM547" t="s" s="2">
-        <v>857</v>
+        <v>851</v>
       </c>
       <c r="AN547" t="s" s="2">
         <v>78</v>
@@ -68549,12 +68564,12 @@
         <v>78</v>
       </c>
     </row>
-    <row r="548" hidden="true">
+    <row r="548">
       <c r="A548" t="s" s="2">
-        <v>1334</v>
+        <v>1336</v>
       </c>
       <c r="B548" t="s" s="2">
-        <v>858</v>
+        <v>852</v>
       </c>
       <c r="C548" s="2"/>
       <c r="D548" t="s" s="2">
@@ -68562,13 +68577,13 @@
       </c>
       <c r="E548" s="2"/>
       <c r="F548" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="G548" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H548" t="s" s="2">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="I548" t="s" s="2">
         <v>78</v>
@@ -68577,20 +68592,18 @@
         <v>78</v>
       </c>
       <c r="K548" t="s" s="2">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="L548" t="s" s="2">
-        <v>859</v>
+        <v>1337</v>
       </c>
       <c r="M548" t="s" s="2">
-        <v>860</v>
+        <v>854</v>
       </c>
       <c r="N548" t="s" s="2">
-        <v>861</v>
-      </c>
-      <c r="O548" t="s" s="2">
-        <v>862</v>
-      </c>
+        <v>855</v>
+      </c>
+      <c r="O548" s="2"/>
       <c r="P548" t="s" s="2">
         <v>78</v>
       </c>
@@ -68614,13 +68627,13 @@
         <v>78</v>
       </c>
       <c r="X548" t="s" s="2">
-        <v>325</v>
+        <v>78</v>
       </c>
       <c r="Y548" t="s" s="2">
-        <v>863</v>
+        <v>78</v>
       </c>
       <c r="Z548" t="s" s="2">
-        <v>864</v>
+        <v>78</v>
       </c>
       <c r="AA548" t="s" s="2">
         <v>78</v>
@@ -68638,7 +68651,7 @@
         <v>78</v>
       </c>
       <c r="AF548" t="s" s="2">
-        <v>858</v>
+        <v>852</v>
       </c>
       <c r="AG548" t="s" s="2">
         <v>79</v>
@@ -68647,7 +68660,7 @@
         <v>91</v>
       </c>
       <c r="AI548" t="s" s="2">
-        <v>78</v>
+        <v>856</v>
       </c>
       <c r="AJ548" t="s" s="2">
         <v>103</v>
@@ -68656,24 +68669,24 @@
         <v>78</v>
       </c>
       <c r="AL548" t="s" s="2">
-        <v>865</v>
+        <v>857</v>
       </c>
       <c r="AM548" t="s" s="2">
-        <v>109</v>
+        <v>857</v>
       </c>
       <c r="AN548" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO548" t="s" s="2">
-        <v>460</v>
+        <v>78</v>
       </c>
     </row>
     <row r="549" hidden="true">
       <c r="A549" t="s" s="2">
-        <v>1335</v>
+        <v>1338</v>
       </c>
       <c r="B549" t="s" s="2">
-        <v>866</v>
+        <v>858</v>
       </c>
       <c r="C549" s="2"/>
       <c r="D549" t="s" s="2">
@@ -68696,19 +68709,19 @@
         <v>78</v>
       </c>
       <c r="K549" t="s" s="2">
-        <v>235</v>
+        <v>171</v>
       </c>
       <c r="L549" t="s" s="2">
-        <v>867</v>
+        <v>859</v>
       </c>
       <c r="M549" t="s" s="2">
-        <v>868</v>
+        <v>860</v>
       </c>
       <c r="N549" t="s" s="2">
-        <v>869</v>
+        <v>861</v>
       </c>
       <c r="O549" t="s" s="2">
-        <v>870</v>
+        <v>862</v>
       </c>
       <c r="P549" t="s" s="2">
         <v>78</v>
@@ -68733,13 +68746,13 @@
         <v>78</v>
       </c>
       <c r="X549" t="s" s="2">
-        <v>175</v>
+        <v>325</v>
       </c>
       <c r="Y549" t="s" s="2">
-        <v>871</v>
+        <v>863</v>
       </c>
       <c r="Z549" t="s" s="2">
-        <v>872</v>
+        <v>864</v>
       </c>
       <c r="AA549" t="s" s="2">
         <v>78</v>
@@ -68757,7 +68770,7 @@
         <v>78</v>
       </c>
       <c r="AF549" t="s" s="2">
-        <v>866</v>
+        <v>858</v>
       </c>
       <c r="AG549" t="s" s="2">
         <v>79</v>
@@ -68775,7 +68788,7 @@
         <v>78</v>
       </c>
       <c r="AL549" t="s" s="2">
-        <v>873</v>
+        <v>865</v>
       </c>
       <c r="AM549" t="s" s="2">
         <v>109</v>
@@ -68784,15 +68797,15 @@
         <v>78</v>
       </c>
       <c r="AO549" t="s" s="2">
-        <v>78</v>
+        <v>460</v>
       </c>
     </row>
     <row r="550" hidden="true">
       <c r="A550" t="s" s="2">
-        <v>1336</v>
+        <v>1339</v>
       </c>
       <c r="B550" t="s" s="2">
-        <v>874</v>
+        <v>866</v>
       </c>
       <c r="C550" s="2"/>
       <c r="D550" t="s" s="2">
@@ -68803,7 +68816,7 @@
         <v>79</v>
       </c>
       <c r="G550" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="H550" t="s" s="2">
         <v>78</v>
@@ -68815,18 +68828,20 @@
         <v>78</v>
       </c>
       <c r="K550" t="s" s="2">
-        <v>797</v>
+        <v>235</v>
       </c>
       <c r="L550" t="s" s="2">
-        <v>875</v>
+        <v>867</v>
       </c>
       <c r="M550" t="s" s="2">
-        <v>876</v>
+        <v>868</v>
       </c>
       <c r="N550" t="s" s="2">
-        <v>877</v>
-      </c>
-      <c r="O550" s="2"/>
+        <v>869</v>
+      </c>
+      <c r="O550" t="s" s="2">
+        <v>870</v>
+      </c>
       <c r="P550" t="s" s="2">
         <v>78</v>
       </c>
@@ -68850,13 +68865,13 @@
         <v>78</v>
       </c>
       <c r="X550" t="s" s="2">
-        <v>78</v>
+        <v>175</v>
       </c>
       <c r="Y550" t="s" s="2">
-        <v>78</v>
+        <v>871</v>
       </c>
       <c r="Z550" t="s" s="2">
-        <v>78</v>
+        <v>872</v>
       </c>
       <c r="AA550" t="s" s="2">
         <v>78</v>
@@ -68874,16 +68889,16 @@
         <v>78</v>
       </c>
       <c r="AF550" t="s" s="2">
-        <v>874</v>
+        <v>866</v>
       </c>
       <c r="AG550" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH550" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI550" t="s" s="2">
-        <v>878</v>
+        <v>78</v>
       </c>
       <c r="AJ550" t="s" s="2">
         <v>103</v>
@@ -68892,10 +68907,10 @@
         <v>78</v>
       </c>
       <c r="AL550" t="s" s="2">
-        <v>879</v>
+        <v>873</v>
       </c>
       <c r="AM550" t="s" s="2">
-        <v>880</v>
+        <v>109</v>
       </c>
       <c r="AN550" t="s" s="2">
         <v>78</v>
@@ -68906,10 +68921,10 @@
     </row>
     <row r="551" hidden="true">
       <c r="A551" t="s" s="2">
-        <v>1337</v>
+        <v>1340</v>
       </c>
       <c r="B551" t="s" s="2">
-        <v>881</v>
+        <v>874</v>
       </c>
       <c r="C551" s="2"/>
       <c r="D551" t="s" s="2">
@@ -68920,7 +68935,7 @@
         <v>79</v>
       </c>
       <c r="G551" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="H551" t="s" s="2">
         <v>78</v>
@@ -68932,20 +68947,18 @@
         <v>78</v>
       </c>
       <c r="K551" t="s" s="2">
-        <v>235</v>
+        <v>797</v>
       </c>
       <c r="L551" t="s" s="2">
-        <v>882</v>
+        <v>875</v>
       </c>
       <c r="M551" t="s" s="2">
-        <v>883</v>
+        <v>876</v>
       </c>
       <c r="N551" t="s" s="2">
-        <v>884</v>
-      </c>
-      <c r="O551" t="s" s="2">
-        <v>885</v>
-      </c>
+        <v>877</v>
+      </c>
+      <c r="O551" s="2"/>
       <c r="P551" t="s" s="2">
         <v>78</v>
       </c>
@@ -68969,13 +68982,13 @@
         <v>78</v>
       </c>
       <c r="X551" t="s" s="2">
-        <v>175</v>
+        <v>78</v>
       </c>
       <c r="Y551" t="s" s="2">
-        <v>886</v>
+        <v>78</v>
       </c>
       <c r="Z551" t="s" s="2">
-        <v>887</v>
+        <v>78</v>
       </c>
       <c r="AA551" t="s" s="2">
         <v>78</v>
@@ -68993,13 +69006,13 @@
         <v>78</v>
       </c>
       <c r="AF551" t="s" s="2">
-        <v>881</v>
+        <v>874</v>
       </c>
       <c r="AG551" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH551" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI551" t="s" s="2">
         <v>878</v>
@@ -69011,10 +69024,10 @@
         <v>78</v>
       </c>
       <c r="AL551" t="s" s="2">
-        <v>888</v>
+        <v>879</v>
       </c>
       <c r="AM551" t="s" s="2">
-        <v>109</v>
+        <v>880</v>
       </c>
       <c r="AN551" t="s" s="2">
         <v>78</v>
@@ -69025,10 +69038,10 @@
     </row>
     <row r="552" hidden="true">
       <c r="A552" t="s" s="2">
-        <v>1338</v>
+        <v>1341</v>
       </c>
       <c r="B552" t="s" s="2">
-        <v>889</v>
+        <v>881</v>
       </c>
       <c r="C552" s="2"/>
       <c r="D552" t="s" s="2">
@@ -69039,7 +69052,7 @@
         <v>79</v>
       </c>
       <c r="G552" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H552" t="s" s="2">
         <v>78</v>
@@ -69051,18 +69064,20 @@
         <v>78</v>
       </c>
       <c r="K552" t="s" s="2">
-        <v>81</v>
+        <v>235</v>
       </c>
       <c r="L552" t="s" s="2">
-        <v>890</v>
+        <v>882</v>
       </c>
       <c r="M552" t="s" s="2">
-        <v>891</v>
+        <v>883</v>
       </c>
       <c r="N552" t="s" s="2">
-        <v>892</v>
-      </c>
-      <c r="O552" s="2"/>
+        <v>884</v>
+      </c>
+      <c r="O552" t="s" s="2">
+        <v>885</v>
+      </c>
       <c r="P552" t="s" s="2">
         <v>78</v>
       </c>
@@ -69086,13 +69101,13 @@
         <v>78</v>
       </c>
       <c r="X552" t="s" s="2">
-        <v>78</v>
+        <v>175</v>
       </c>
       <c r="Y552" t="s" s="2">
-        <v>78</v>
+        <v>886</v>
       </c>
       <c r="Z552" t="s" s="2">
-        <v>78</v>
+        <v>887</v>
       </c>
       <c r="AA552" t="s" s="2">
         <v>78</v>
@@ -69110,16 +69125,16 @@
         <v>78</v>
       </c>
       <c r="AF552" t="s" s="2">
-        <v>889</v>
+        <v>881</v>
       </c>
       <c r="AG552" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH552" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI552" t="s" s="2">
-        <v>856</v>
+        <v>878</v>
       </c>
       <c r="AJ552" t="s" s="2">
         <v>103</v>
@@ -69128,20 +69143,137 @@
         <v>78</v>
       </c>
       <c r="AL552" t="s" s="2">
+        <v>888</v>
+      </c>
+      <c r="AM552" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="AN552" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO552" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="553" hidden="true">
+      <c r="A553" t="s" s="2">
+        <v>1342</v>
+      </c>
+      <c r="B553" t="s" s="2">
+        <v>889</v>
+      </c>
+      <c r="C553" s="2"/>
+      <c r="D553" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E553" s="2"/>
+      <c r="F553" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G553" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H553" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I553" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J553" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K553" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="L553" t="s" s="2">
+        <v>890</v>
+      </c>
+      <c r="M553" t="s" s="2">
+        <v>891</v>
+      </c>
+      <c r="N553" t="s" s="2">
+        <v>892</v>
+      </c>
+      <c r="O553" s="2"/>
+      <c r="P553" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q553" s="2"/>
+      <c r="R553" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S553" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T553" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U553" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V553" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W553" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X553" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y553" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z553" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA553" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB553" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC553" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD553" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE553" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF553" t="s" s="2">
+        <v>889</v>
+      </c>
+      <c r="AG553" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH553" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI553" t="s" s="2">
+        <v>856</v>
+      </c>
+      <c r="AJ553" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK553" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL553" t="s" s="2">
         <v>818</v>
       </c>
-      <c r="AM552" t="s" s="2">
+      <c r="AM553" t="s" s="2">
         <v>893</v>
       </c>
-      <c r="AN552" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO552" t="s" s="2">
+      <c r="AN553" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO553" t="s" s="2">
         <v>78</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO552">
+  <autoFilter ref="A1:AO553">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -69151,7 +69283,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI551">
+  <conditionalFormatting sqref="A2:AI552">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/qaErrors/ig/StructureDefinition-fr-composition-document-ips.xlsx
+++ b/qaErrors/ig/StructureDefinition-fr-composition-document-ips.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20476" uniqueCount="1343">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20476" uniqueCount="1344">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-24T11:21:48+00:00</t>
+    <t>2026-09-24T12:14:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -3442,7 +3442,7 @@
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
   &lt;coding&gt;
     &lt;system value="http://loinc.org"/&gt;
-    &lt;code value="11369-9"/&gt;
+    &lt;code value="11369-6"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
   </si>
@@ -3873,6 +3873,10 @@
   </si>
   <si>
     <t>Composition.section:sectionPregnancyHistory.entry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">profile:resolve()}
+</t>
   </si>
   <si>
     <t>Composition.section:sectionPregnancyHistory.entry:historiqueGrossesse</t>
@@ -60665,7 +60669,7 @@
         <v>78</v>
       </c>
       <c r="AB480" t="s" s="2">
-        <v>915</v>
+        <v>1225</v>
       </c>
       <c r="AC480" s="2"/>
       <c r="AD480" t="s" s="2">
@@ -60707,13 +60711,13 @@
     </row>
     <row r="481" hidden="true">
       <c r="A481" t="s" s="2">
-        <v>1225</v>
+        <v>1226</v>
       </c>
       <c r="B481" t="s" s="2">
         <v>874</v>
       </c>
       <c r="C481" t="s" s="2">
-        <v>1226</v>
+        <v>1227</v>
       </c>
       <c r="D481" t="s" s="2">
         <v>78</v>
@@ -60735,10 +60739,10 @@
         <v>78</v>
       </c>
       <c r="K481" t="s" s="2">
-        <v>1227</v>
+        <v>1228</v>
       </c>
       <c r="L481" t="s" s="2">
-        <v>1228</v>
+        <v>1229</v>
       </c>
       <c r="M481" t="s" s="2">
         <v>876</v>
@@ -60826,13 +60830,13 @@
     </row>
     <row r="482" hidden="true">
       <c r="A482" t="s" s="2">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="B482" t="s" s="2">
         <v>874</v>
       </c>
       <c r="C482" t="s" s="2">
-        <v>1230</v>
+        <v>1231</v>
       </c>
       <c r="D482" t="s" s="2">
         <v>78</v>
@@ -60854,10 +60858,10 @@
         <v>78</v>
       </c>
       <c r="K482" t="s" s="2">
-        <v>1231</v>
+        <v>1232</v>
       </c>
       <c r="L482" t="s" s="2">
-        <v>1232</v>
+        <v>1233</v>
       </c>
       <c r="M482" t="s" s="2">
         <v>876</v>
@@ -60945,7 +60949,7 @@
     </row>
     <row r="483">
       <c r="A483" t="s" s="2">
-        <v>1233</v>
+        <v>1234</v>
       </c>
       <c r="B483" t="s" s="2">
         <v>881</v>
@@ -61062,7 +61066,7 @@
     </row>
     <row r="484" hidden="true">
       <c r="A484" t="s" s="2">
-        <v>1234</v>
+        <v>1235</v>
       </c>
       <c r="B484" t="s" s="2">
         <v>889</v>
@@ -61179,13 +61183,13 @@
     </row>
     <row r="485">
       <c r="A485" t="s" s="2">
-        <v>1235</v>
+        <v>1236</v>
       </c>
       <c r="B485" t="s" s="2">
         <v>812</v>
       </c>
       <c r="C485" t="s" s="2">
-        <v>1236</v>
+        <v>1237</v>
       </c>
       <c r="D485" t="s" s="2">
         <v>78</v>
@@ -61210,10 +61214,10 @@
         <v>568</v>
       </c>
       <c r="L485" t="s" s="2">
-        <v>1237</v>
+        <v>1238</v>
       </c>
       <c r="M485" t="s" s="2">
-        <v>1238</v>
+        <v>1239</v>
       </c>
       <c r="N485" s="2"/>
       <c r="O485" s="2"/>
@@ -61296,7 +61300,7 @@
     </row>
     <row r="486" hidden="true">
       <c r="A486" t="s" s="2">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="B486" t="s" s="2">
         <v>820</v>
@@ -61411,7 +61415,7 @@
     </row>
     <row r="487" hidden="true">
       <c r="A487" t="s" s="2">
-        <v>1240</v>
+        <v>1241</v>
       </c>
       <c r="B487" t="s" s="2">
         <v>821</v>
@@ -61524,7 +61528,7 @@
     </row>
     <row r="488" hidden="true">
       <c r="A488" t="s" s="2">
-        <v>1241</v>
+        <v>1242</v>
       </c>
       <c r="B488" t="s" s="2">
         <v>821</v>
@@ -61641,7 +61645,7 @@
     </row>
     <row r="489" hidden="true">
       <c r="A489" t="s" s="2">
-        <v>1242</v>
+        <v>1243</v>
       </c>
       <c r="B489" t="s" s="2">
         <v>821</v>
@@ -61760,7 +61764,7 @@
     </row>
     <row r="490" hidden="true">
       <c r="A490" t="s" s="2">
-        <v>1243</v>
+        <v>1244</v>
       </c>
       <c r="B490" t="s" s="2">
         <v>830</v>
@@ -61879,7 +61883,7 @@
     </row>
     <row r="491">
       <c r="A491" t="s" s="2">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="B491" t="s" s="2">
         <v>831</v>
@@ -61908,7 +61912,7 @@
         <v>105</v>
       </c>
       <c r="L491" t="s" s="2">
-        <v>1245</v>
+        <v>1246</v>
       </c>
       <c r="M491" t="s" s="2">
         <v>834</v>
@@ -61998,7 +62002,7 @@
     </row>
     <row r="492">
       <c r="A492" t="s" s="2">
-        <v>1246</v>
+        <v>1247</v>
       </c>
       <c r="B492" t="s" s="2">
         <v>837</v>
@@ -62046,7 +62050,7 @@
         <v>78</v>
       </c>
       <c r="S492" t="s" s="2">
-        <v>1247</v>
+        <v>1248</v>
       </c>
       <c r="T492" t="s" s="2">
         <v>78</v>
@@ -62115,7 +62119,7 @@
     </row>
     <row r="493" hidden="true">
       <c r="A493" t="s" s="2">
-        <v>1248</v>
+        <v>1249</v>
       </c>
       <c r="B493" t="s" s="2">
         <v>843</v>
@@ -62232,7 +62236,7 @@
     </row>
     <row r="494" hidden="true">
       <c r="A494" t="s" s="2">
-        <v>1249</v>
+        <v>1250</v>
       </c>
       <c r="B494" t="s" s="2">
         <v>847</v>
@@ -62349,7 +62353,7 @@
     </row>
     <row r="495">
       <c r="A495" t="s" s="2">
-        <v>1250</v>
+        <v>1251</v>
       </c>
       <c r="B495" t="s" s="2">
         <v>852</v>
@@ -62378,7 +62382,7 @@
         <v>182</v>
       </c>
       <c r="L495" t="s" s="2">
-        <v>1251</v>
+        <v>1252</v>
       </c>
       <c r="M495" t="s" s="2">
         <v>854</v>
@@ -62466,7 +62470,7 @@
     </row>
     <row r="496" hidden="true">
       <c r="A496" t="s" s="2">
-        <v>1252</v>
+        <v>1253</v>
       </c>
       <c r="B496" t="s" s="2">
         <v>858</v>
@@ -62585,7 +62589,7 @@
     </row>
     <row r="497" hidden="true">
       <c r="A497" t="s" s="2">
-        <v>1253</v>
+        <v>1254</v>
       </c>
       <c r="B497" t="s" s="2">
         <v>866</v>
@@ -62704,7 +62708,7 @@
     </row>
     <row r="498" hidden="true">
       <c r="A498" t="s" s="2">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="B498" t="s" s="2">
         <v>874</v>
@@ -62819,13 +62823,13 @@
     </row>
     <row r="499" hidden="true">
       <c r="A499" t="s" s="2">
-        <v>1255</v>
+        <v>1256</v>
       </c>
       <c r="B499" t="s" s="2">
         <v>874</v>
       </c>
       <c r="C499" t="s" s="2">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="D499" t="s" s="2">
         <v>78</v>
@@ -62847,10 +62851,10 @@
         <v>78</v>
       </c>
       <c r="K499" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="L499" t="s" s="2">
-        <v>1258</v>
+        <v>1259</v>
       </c>
       <c r="M499" t="s" s="2">
         <v>876</v>
@@ -62938,13 +62942,13 @@
     </row>
     <row r="500" hidden="true">
       <c r="A500" t="s" s="2">
-        <v>1259</v>
+        <v>1260</v>
       </c>
       <c r="B500" t="s" s="2">
         <v>874</v>
       </c>
       <c r="C500" t="s" s="2">
-        <v>1260</v>
+        <v>1261</v>
       </c>
       <c r="D500" t="s" s="2">
         <v>78</v>
@@ -62966,10 +62970,10 @@
         <v>78</v>
       </c>
       <c r="K500" t="s" s="2">
-        <v>1261</v>
+        <v>1262</v>
       </c>
       <c r="L500" t="s" s="2">
-        <v>1262</v>
+        <v>1263</v>
       </c>
       <c r="M500" t="s" s="2">
         <v>876</v>
@@ -63057,13 +63061,13 @@
     </row>
     <row r="501" hidden="true">
       <c r="A501" t="s" s="2">
-        <v>1263</v>
+        <v>1264</v>
       </c>
       <c r="B501" t="s" s="2">
         <v>874</v>
       </c>
       <c r="C501" t="s" s="2">
-        <v>1264</v>
+        <v>1265</v>
       </c>
       <c r="D501" t="s" s="2">
         <v>78</v>
@@ -63085,10 +63089,10 @@
         <v>78</v>
       </c>
       <c r="K501" t="s" s="2">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="L501" t="s" s="2">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="M501" t="s" s="2">
         <v>876</v>
@@ -63176,7 +63180,7 @@
     </row>
     <row r="502">
       <c r="A502" t="s" s="2">
-        <v>1267</v>
+        <v>1268</v>
       </c>
       <c r="B502" t="s" s="2">
         <v>881</v>
@@ -63293,7 +63297,7 @@
     </row>
     <row r="503" hidden="true">
       <c r="A503" t="s" s="2">
-        <v>1268</v>
+        <v>1269</v>
       </c>
       <c r="B503" t="s" s="2">
         <v>889</v>
@@ -63410,13 +63414,13 @@
     </row>
     <row r="504">
       <c r="A504" t="s" s="2">
-        <v>1269</v>
+        <v>1270</v>
       </c>
       <c r="B504" t="s" s="2">
         <v>812</v>
       </c>
       <c r="C504" t="s" s="2">
-        <v>1270</v>
+        <v>1271</v>
       </c>
       <c r="D504" t="s" s="2">
         <v>78</v>
@@ -63441,10 +63445,10 @@
         <v>568</v>
       </c>
       <c r="L504" t="s" s="2">
-        <v>1271</v>
+        <v>1272</v>
       </c>
       <c r="M504" t="s" s="2">
-        <v>1272</v>
+        <v>1273</v>
       </c>
       <c r="N504" s="2"/>
       <c r="O504" s="2"/>
@@ -63527,7 +63531,7 @@
     </row>
     <row r="505" hidden="true">
       <c r="A505" t="s" s="2">
-        <v>1273</v>
+        <v>1274</v>
       </c>
       <c r="B505" t="s" s="2">
         <v>820</v>
@@ -63642,7 +63646,7 @@
     </row>
     <row r="506" hidden="true">
       <c r="A506" t="s" s="2">
-        <v>1274</v>
+        <v>1275</v>
       </c>
       <c r="B506" t="s" s="2">
         <v>821</v>
@@ -63755,7 +63759,7 @@
     </row>
     <row r="507" hidden="true">
       <c r="A507" t="s" s="2">
-        <v>1275</v>
+        <v>1276</v>
       </c>
       <c r="B507" t="s" s="2">
         <v>821</v>
@@ -63872,7 +63876,7 @@
     </row>
     <row r="508" hidden="true">
       <c r="A508" t="s" s="2">
-        <v>1276</v>
+        <v>1277</v>
       </c>
       <c r="B508" t="s" s="2">
         <v>821</v>
@@ -63991,7 +63995,7 @@
     </row>
     <row r="509" hidden="true">
       <c r="A509" t="s" s="2">
-        <v>1277</v>
+        <v>1278</v>
       </c>
       <c r="B509" t="s" s="2">
         <v>830</v>
@@ -64110,7 +64114,7 @@
     </row>
     <row r="510">
       <c r="A510" t="s" s="2">
-        <v>1278</v>
+        <v>1279</v>
       </c>
       <c r="B510" t="s" s="2">
         <v>831</v>
@@ -64139,7 +64143,7 @@
         <v>105</v>
       </c>
       <c r="L510" t="s" s="2">
-        <v>1279</v>
+        <v>1280</v>
       </c>
       <c r="M510" t="s" s="2">
         <v>834</v>
@@ -64229,7 +64233,7 @@
     </row>
     <row r="511">
       <c r="A511" t="s" s="2">
-        <v>1280</v>
+        <v>1281</v>
       </c>
       <c r="B511" t="s" s="2">
         <v>837</v>
@@ -64277,7 +64281,7 @@
         <v>78</v>
       </c>
       <c r="S511" t="s" s="2">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="T511" t="s" s="2">
         <v>78</v>
@@ -64346,7 +64350,7 @@
     </row>
     <row r="512" hidden="true">
       <c r="A512" t="s" s="2">
-        <v>1282</v>
+        <v>1283</v>
       </c>
       <c r="B512" t="s" s="2">
         <v>843</v>
@@ -64463,7 +64467,7 @@
     </row>
     <row r="513" hidden="true">
       <c r="A513" t="s" s="2">
-        <v>1283</v>
+        <v>1284</v>
       </c>
       <c r="B513" t="s" s="2">
         <v>847</v>
@@ -64580,7 +64584,7 @@
     </row>
     <row r="514">
       <c r="A514" t="s" s="2">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="B514" t="s" s="2">
         <v>852</v>
@@ -64609,7 +64613,7 @@
         <v>182</v>
       </c>
       <c r="L514" t="s" s="2">
-        <v>1285</v>
+        <v>1286</v>
       </c>
       <c r="M514" t="s" s="2">
         <v>854</v>
@@ -64697,7 +64701,7 @@
     </row>
     <row r="515" hidden="true">
       <c r="A515" t="s" s="2">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="B515" t="s" s="2">
         <v>858</v>
@@ -64816,7 +64820,7 @@
     </row>
     <row r="516" hidden="true">
       <c r="A516" t="s" s="2">
-        <v>1287</v>
+        <v>1288</v>
       </c>
       <c r="B516" t="s" s="2">
         <v>866</v>
@@ -64935,7 +64939,7 @@
     </row>
     <row r="517" hidden="true">
       <c r="A517" t="s" s="2">
-        <v>1288</v>
+        <v>1289</v>
       </c>
       <c r="B517" t="s" s="2">
         <v>874</v>
@@ -65050,13 +65054,13 @@
     </row>
     <row r="518" hidden="true">
       <c r="A518" t="s" s="2">
-        <v>1289</v>
+        <v>1290</v>
       </c>
       <c r="B518" t="s" s="2">
         <v>874</v>
       </c>
       <c r="C518" t="s" s="2">
-        <v>1290</v>
+        <v>1291</v>
       </c>
       <c r="D518" t="s" s="2">
         <v>78</v>
@@ -65078,10 +65082,10 @@
         <v>78</v>
       </c>
       <c r="K518" t="s" s="2">
-        <v>1291</v>
+        <v>1292</v>
       </c>
       <c r="L518" t="s" s="2">
-        <v>1292</v>
+        <v>1293</v>
       </c>
       <c r="M518" t="s" s="2">
         <v>876</v>
@@ -65169,7 +65173,7 @@
     </row>
     <row r="519">
       <c r="A519" t="s" s="2">
-        <v>1293</v>
+        <v>1294</v>
       </c>
       <c r="B519" t="s" s="2">
         <v>881</v>
@@ -65286,7 +65290,7 @@
     </row>
     <row r="520" hidden="true">
       <c r="A520" t="s" s="2">
-        <v>1294</v>
+        <v>1295</v>
       </c>
       <c r="B520" t="s" s="2">
         <v>889</v>
@@ -65403,13 +65407,13 @@
     </row>
     <row r="521">
       <c r="A521" t="s" s="2">
-        <v>1295</v>
+        <v>1296</v>
       </c>
       <c r="B521" t="s" s="2">
         <v>812</v>
       </c>
       <c r="C521" t="s" s="2">
-        <v>1296</v>
+        <v>1297</v>
       </c>
       <c r="D521" t="s" s="2">
         <v>78</v>
@@ -65434,10 +65438,10 @@
         <v>568</v>
       </c>
       <c r="L521" t="s" s="2">
-        <v>1297</v>
+        <v>1298</v>
       </c>
       <c r="M521" t="s" s="2">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="N521" s="2"/>
       <c r="O521" s="2"/>
@@ -65520,7 +65524,7 @@
     </row>
     <row r="522" hidden="true">
       <c r="A522" t="s" s="2">
-        <v>1299</v>
+        <v>1300</v>
       </c>
       <c r="B522" t="s" s="2">
         <v>820</v>
@@ -65635,7 +65639,7 @@
     </row>
     <row r="523" hidden="true">
       <c r="A523" t="s" s="2">
-        <v>1300</v>
+        <v>1301</v>
       </c>
       <c r="B523" t="s" s="2">
         <v>821</v>
@@ -65748,7 +65752,7 @@
     </row>
     <row r="524" hidden="true">
       <c r="A524" t="s" s="2">
-        <v>1301</v>
+        <v>1302</v>
       </c>
       <c r="B524" t="s" s="2">
         <v>821</v>
@@ -65865,7 +65869,7 @@
     </row>
     <row r="525" hidden="true">
       <c r="A525" t="s" s="2">
-        <v>1302</v>
+        <v>1303</v>
       </c>
       <c r="B525" t="s" s="2">
         <v>821</v>
@@ -65984,7 +65988,7 @@
     </row>
     <row r="526" hidden="true">
       <c r="A526" t="s" s="2">
-        <v>1303</v>
+        <v>1304</v>
       </c>
       <c r="B526" t="s" s="2">
         <v>830</v>
@@ -66103,7 +66107,7 @@
     </row>
     <row r="527">
       <c r="A527" t="s" s="2">
-        <v>1304</v>
+        <v>1305</v>
       </c>
       <c r="B527" t="s" s="2">
         <v>831</v>
@@ -66132,7 +66136,7 @@
         <v>105</v>
       </c>
       <c r="L527" t="s" s="2">
-        <v>1305</v>
+        <v>1306</v>
       </c>
       <c r="M527" t="s" s="2">
         <v>834</v>
@@ -66222,7 +66226,7 @@
     </row>
     <row r="528">
       <c r="A528" t="s" s="2">
-        <v>1306</v>
+        <v>1307</v>
       </c>
       <c r="B528" t="s" s="2">
         <v>837</v>
@@ -66270,7 +66274,7 @@
         <v>78</v>
       </c>
       <c r="S528" t="s" s="2">
-        <v>1307</v>
+        <v>1308</v>
       </c>
       <c r="T528" t="s" s="2">
         <v>78</v>
@@ -66339,7 +66343,7 @@
     </row>
     <row r="529" hidden="true">
       <c r="A529" t="s" s="2">
-        <v>1308</v>
+        <v>1309</v>
       </c>
       <c r="B529" t="s" s="2">
         <v>843</v>
@@ -66456,7 +66460,7 @@
     </row>
     <row r="530" hidden="true">
       <c r="A530" t="s" s="2">
-        <v>1309</v>
+        <v>1310</v>
       </c>
       <c r="B530" t="s" s="2">
         <v>847</v>
@@ -66573,7 +66577,7 @@
     </row>
     <row r="531">
       <c r="A531" t="s" s="2">
-        <v>1310</v>
+        <v>1311</v>
       </c>
       <c r="B531" t="s" s="2">
         <v>852</v>
@@ -66602,7 +66606,7 @@
         <v>182</v>
       </c>
       <c r="L531" t="s" s="2">
-        <v>1311</v>
+        <v>1312</v>
       </c>
       <c r="M531" t="s" s="2">
         <v>854</v>
@@ -66690,7 +66694,7 @@
     </row>
     <row r="532" hidden="true">
       <c r="A532" t="s" s="2">
-        <v>1312</v>
+        <v>1313</v>
       </c>
       <c r="B532" t="s" s="2">
         <v>858</v>
@@ -66809,7 +66813,7 @@
     </row>
     <row r="533" hidden="true">
       <c r="A533" t="s" s="2">
-        <v>1313</v>
+        <v>1314</v>
       </c>
       <c r="B533" t="s" s="2">
         <v>866</v>
@@ -66928,7 +66932,7 @@
     </row>
     <row r="534" hidden="true">
       <c r="A534" t="s" s="2">
-        <v>1314</v>
+        <v>1315</v>
       </c>
       <c r="B534" t="s" s="2">
         <v>874</v>
@@ -67043,13 +67047,13 @@
     </row>
     <row r="535" hidden="true">
       <c r="A535" t="s" s="2">
-        <v>1315</v>
+        <v>1316</v>
       </c>
       <c r="B535" t="s" s="2">
         <v>874</v>
       </c>
       <c r="C535" t="s" s="2">
-        <v>1316</v>
+        <v>1317</v>
       </c>
       <c r="D535" t="s" s="2">
         <v>78</v>
@@ -67071,10 +67075,10 @@
         <v>78</v>
       </c>
       <c r="K535" t="s" s="2">
-        <v>1317</v>
+        <v>1318</v>
       </c>
       <c r="L535" t="s" s="2">
-        <v>1318</v>
+        <v>1319</v>
       </c>
       <c r="M535" t="s" s="2">
         <v>876</v>
@@ -67162,7 +67166,7 @@
     </row>
     <row r="536">
       <c r="A536" t="s" s="2">
-        <v>1319</v>
+        <v>1320</v>
       </c>
       <c r="B536" t="s" s="2">
         <v>881</v>
@@ -67279,7 +67283,7 @@
     </row>
     <row r="537" hidden="true">
       <c r="A537" t="s" s="2">
-        <v>1320</v>
+        <v>1321</v>
       </c>
       <c r="B537" t="s" s="2">
         <v>889</v>
@@ -67396,13 +67400,13 @@
     </row>
     <row r="538">
       <c r="A538" t="s" s="2">
-        <v>1321</v>
+        <v>1322</v>
       </c>
       <c r="B538" t="s" s="2">
         <v>812</v>
       </c>
       <c r="C538" t="s" s="2">
-        <v>1322</v>
+        <v>1323</v>
       </c>
       <c r="D538" t="s" s="2">
         <v>78</v>
@@ -67427,10 +67431,10 @@
         <v>568</v>
       </c>
       <c r="L538" t="s" s="2">
-        <v>1323</v>
+        <v>1324</v>
       </c>
       <c r="M538" t="s" s="2">
-        <v>1324</v>
+        <v>1325</v>
       </c>
       <c r="N538" s="2"/>
       <c r="O538" s="2"/>
@@ -67513,7 +67517,7 @@
     </row>
     <row r="539" hidden="true">
       <c r="A539" t="s" s="2">
-        <v>1325</v>
+        <v>1326</v>
       </c>
       <c r="B539" t="s" s="2">
         <v>820</v>
@@ -67628,7 +67632,7 @@
     </row>
     <row r="540" hidden="true">
       <c r="A540" t="s" s="2">
-        <v>1326</v>
+        <v>1327</v>
       </c>
       <c r="B540" t="s" s="2">
         <v>821</v>
@@ -67741,7 +67745,7 @@
     </row>
     <row r="541" hidden="true">
       <c r="A541" t="s" s="2">
-        <v>1327</v>
+        <v>1328</v>
       </c>
       <c r="B541" t="s" s="2">
         <v>821</v>
@@ -67858,7 +67862,7 @@
     </row>
     <row r="542" hidden="true">
       <c r="A542" t="s" s="2">
-        <v>1328</v>
+        <v>1329</v>
       </c>
       <c r="B542" t="s" s="2">
         <v>821</v>
@@ -67977,7 +67981,7 @@
     </row>
     <row r="543" hidden="true">
       <c r="A543" t="s" s="2">
-        <v>1329</v>
+        <v>1330</v>
       </c>
       <c r="B543" t="s" s="2">
         <v>830</v>
@@ -68096,7 +68100,7 @@
     </row>
     <row r="544">
       <c r="A544" t="s" s="2">
-        <v>1330</v>
+        <v>1331</v>
       </c>
       <c r="B544" t="s" s="2">
         <v>831</v>
@@ -68125,7 +68129,7 @@
         <v>105</v>
       </c>
       <c r="L544" t="s" s="2">
-        <v>1331</v>
+        <v>1332</v>
       </c>
       <c r="M544" t="s" s="2">
         <v>834</v>
@@ -68215,7 +68219,7 @@
     </row>
     <row r="545">
       <c r="A545" t="s" s="2">
-        <v>1332</v>
+        <v>1333</v>
       </c>
       <c r="B545" t="s" s="2">
         <v>837</v>
@@ -68263,7 +68267,7 @@
         <v>78</v>
       </c>
       <c r="S545" t="s" s="2">
-        <v>1333</v>
+        <v>1334</v>
       </c>
       <c r="T545" t="s" s="2">
         <v>78</v>
@@ -68332,7 +68336,7 @@
     </row>
     <row r="546" hidden="true">
       <c r="A546" t="s" s="2">
-        <v>1334</v>
+        <v>1335</v>
       </c>
       <c r="B546" t="s" s="2">
         <v>843</v>
@@ -68449,7 +68453,7 @@
     </row>
     <row r="547" hidden="true">
       <c r="A547" t="s" s="2">
-        <v>1335</v>
+        <v>1336</v>
       </c>
       <c r="B547" t="s" s="2">
         <v>847</v>
@@ -68566,7 +68570,7 @@
     </row>
     <row r="548">
       <c r="A548" t="s" s="2">
-        <v>1336</v>
+        <v>1337</v>
       </c>
       <c r="B548" t="s" s="2">
         <v>852</v>
@@ -68595,7 +68599,7 @@
         <v>182</v>
       </c>
       <c r="L548" t="s" s="2">
-        <v>1337</v>
+        <v>1338</v>
       </c>
       <c r="M548" t="s" s="2">
         <v>854</v>
@@ -68683,7 +68687,7 @@
     </row>
     <row r="549" hidden="true">
       <c r="A549" t="s" s="2">
-        <v>1338</v>
+        <v>1339</v>
       </c>
       <c r="B549" t="s" s="2">
         <v>858</v>
@@ -68802,7 +68806,7 @@
     </row>
     <row r="550" hidden="true">
       <c r="A550" t="s" s="2">
-        <v>1339</v>
+        <v>1340</v>
       </c>
       <c r="B550" t="s" s="2">
         <v>866</v>
@@ -68921,7 +68925,7 @@
     </row>
     <row r="551" hidden="true">
       <c r="A551" t="s" s="2">
-        <v>1340</v>
+        <v>1341</v>
       </c>
       <c r="B551" t="s" s="2">
         <v>874</v>
@@ -69038,7 +69042,7 @@
     </row>
     <row r="552" hidden="true">
       <c r="A552" t="s" s="2">
-        <v>1341</v>
+        <v>1342</v>
       </c>
       <c r="B552" t="s" s="2">
         <v>881</v>
@@ -69157,7 +69161,7 @@
     </row>
     <row r="553" hidden="true">
       <c r="A553" t="s" s="2">
-        <v>1342</v>
+        <v>1343</v>
       </c>
       <c r="B553" t="s" s="2">
         <v>889</v>

--- a/qaErrors/ig/StructureDefinition-fr-composition-document-ips.xlsx
+++ b/qaErrors/ig/StructureDefinition-fr-composition-document-ips.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-24T12:14:38+00:00</t>
+    <t>2026-09-25T08:12:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
